--- a/research/traditional_assets/database/data/chile/chile_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_farming_agriculture.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0779431043872372</v>
+        <v>0.07776550800539166</v>
       </c>
       <c r="C2">
-        <v>214.0426011833571</v>
+        <v>212.4827930791475</v>
       </c>
       <c r="D2">
-        <v>195.9426011833571</v>
+        <v>196.6647930791475</v>
       </c>
       <c r="E2">
-        <v>-120.6</v>
+        <v>-118.318</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.282</v>
       </c>
       <c r="G2">
         <v>18.1</v>
@@ -1451,28 +1451,28 @@
         <v>21.35</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1147846</v>
       </c>
       <c r="N2">
-        <v>21.35</v>
+        <v>21.2352154</v>
       </c>
       <c r="O2">
-        <v>5.764500000000001</v>
+        <v>5.733508158000001</v>
       </c>
       <c r="P2">
-        <v>15.5855</v>
+        <v>15.501707242</v>
       </c>
       <c r="Q2">
-        <v>26.9855</v>
+        <v>26.901707242</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0779431043872372</v>
+        <v>0.07818011919736531</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.59305325452791</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>186.0005610508727</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07776550800539166</v>
+        <v>0.07758791162354611</v>
       </c>
       <c r="C3">
-        <v>212.4827930791475</v>
+        <v>210.9283282803458</v>
       </c>
       <c r="D3">
-        <v>196.6647930791475</v>
+        <v>197.3923282803458</v>
       </c>
       <c r="E3">
-        <v>-118.318</v>
+        <v>-116.036</v>
       </c>
       <c r="F3">
-        <v>2.282</v>
+        <v>4.564</v>
       </c>
       <c r="G3">
         <v>18.1</v>
@@ -1533,28 +1533,28 @@
         <v>21.35</v>
       </c>
       <c r="M3">
-        <v>0.1147846</v>
+        <v>0.2295692</v>
       </c>
       <c r="N3">
-        <v>21.2352154</v>
+        <v>21.1204308</v>
       </c>
       <c r="O3">
-        <v>5.733508158000001</v>
+        <v>5.702516316000001</v>
       </c>
       <c r="P3">
-        <v>15.501707242</v>
+        <v>15.417914484</v>
       </c>
       <c r="Q3">
-        <v>26.901707242</v>
+        <v>26.817914484</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07818011919736531</v>
+        <v>0.07842197104443481</v>
       </c>
       <c r="T3">
-        <v>0.59305325452791</v>
+        <v>0.5974828560418484</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>186.0005610508727</v>
+        <v>93.00028052543634</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07758791162354611</v>
+        <v>0.07741031524170057</v>
       </c>
       <c r="C4">
-        <v>210.9283282803458</v>
+        <v>209.3792663076806</v>
       </c>
       <c r="D4">
-        <v>197.3923282803458</v>
+        <v>198.1252663076806</v>
       </c>
       <c r="E4">
-        <v>-116.036</v>
+        <v>-113.754</v>
       </c>
       <c r="F4">
-        <v>4.564</v>
+        <v>6.845999999999999</v>
       </c>
       <c r="G4">
         <v>18.1</v>
@@ -1615,28 +1615,28 @@
         <v>21.35</v>
       </c>
       <c r="M4">
-        <v>0.2295692</v>
+        <v>0.3443537999999999</v>
       </c>
       <c r="N4">
-        <v>21.1204308</v>
+        <v>21.0056462</v>
       </c>
       <c r="O4">
-        <v>5.702516316000001</v>
+        <v>5.671524474000001</v>
       </c>
       <c r="P4">
-        <v>15.417914484</v>
+        <v>15.334121726</v>
       </c>
       <c r="Q4">
-        <v>26.817914484</v>
+        <v>26.734121726</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07842197104443481</v>
+        <v>0.07866880952752636</v>
       </c>
       <c r="T4">
-        <v>0.5974828560418484</v>
+        <v>0.6020037895457648</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>93.00028052543634</v>
+        <v>62.00018701695758</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07741031524170057</v>
+        <v>0.07723271885985503</v>
       </c>
       <c r="C5">
-        <v>209.3792663076806</v>
+        <v>207.8356675692013</v>
       </c>
       <c r="D5">
-        <v>198.1252663076806</v>
+        <v>198.8636675692013</v>
       </c>
       <c r="E5">
-        <v>-113.754</v>
+        <v>-111.472</v>
       </c>
       <c r="F5">
-        <v>6.845999999999999</v>
+        <v>9.128</v>
       </c>
       <c r="G5">
         <v>18.1</v>
@@ -1697,28 +1697,28 @@
         <v>21.35</v>
       </c>
       <c r="M5">
-        <v>0.3443537999999999</v>
+        <v>0.4591384</v>
       </c>
       <c r="N5">
-        <v>21.0056462</v>
+        <v>20.8908616</v>
       </c>
       <c r="O5">
-        <v>5.671524474000001</v>
+        <v>5.640532632</v>
       </c>
       <c r="P5">
-        <v>15.334121726</v>
+        <v>15.250328968</v>
       </c>
       <c r="Q5">
-        <v>26.734121726</v>
+        <v>26.650328968</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07866880952752636</v>
+        <v>0.07892079047901565</v>
       </c>
       <c r="T5">
-        <v>0.6020037895457648</v>
+        <v>0.6066189091643464</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>62.00018701695758</v>
+        <v>46.50014026271817</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07723271885985503</v>
+        <v>0.07705512247800948</v>
       </c>
       <c r="C6">
-        <v>207.8356675692013</v>
+        <v>206.2975933768755</v>
       </c>
       <c r="D6">
-        <v>198.8636675692013</v>
+        <v>199.6075933768755</v>
       </c>
       <c r="E6">
-        <v>-111.472</v>
+        <v>-109.19</v>
       </c>
       <c r="F6">
-        <v>9.128</v>
+        <v>11.41</v>
       </c>
       <c r="G6">
         <v>18.1</v>
@@ -1779,28 +1779,28 @@
         <v>21.35</v>
       </c>
       <c r="M6">
-        <v>0.4591384</v>
+        <v>0.573923</v>
       </c>
       <c r="N6">
-        <v>20.8908616</v>
+        <v>20.776077</v>
       </c>
       <c r="O6">
-        <v>5.640532632</v>
+        <v>5.60954079</v>
       </c>
       <c r="P6">
-        <v>15.250328968</v>
+        <v>15.16653621</v>
       </c>
       <c r="Q6">
-        <v>26.650328968</v>
+        <v>26.56653621</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07892079047901565</v>
+        <v>0.07917807629264156</v>
       </c>
       <c r="T6">
-        <v>0.6066189091643464</v>
+        <v>0.6113311891959504</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>46.50014026271817</v>
+        <v>37.20011221017454</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07705512247800948</v>
+        <v>0.07687752609616395</v>
       </c>
       <c r="C7">
-        <v>206.2975933768755</v>
+        <v>204.7651059635592</v>
       </c>
       <c r="D7">
-        <v>199.6075933768755</v>
+        <v>200.3571059635592</v>
       </c>
       <c r="E7">
-        <v>-109.19</v>
+        <v>-106.908</v>
       </c>
       <c r="F7">
-        <v>11.41</v>
+        <v>13.692</v>
       </c>
       <c r="G7">
         <v>18.1</v>
@@ -1861,28 +1861,28 @@
         <v>21.35</v>
       </c>
       <c r="M7">
-        <v>0.573923</v>
+        <v>0.6887076</v>
       </c>
       <c r="N7">
-        <v>20.776077</v>
+        <v>20.6612924</v>
       </c>
       <c r="O7">
-        <v>5.60954079</v>
+        <v>5.578548948000001</v>
       </c>
       <c r="P7">
-        <v>15.16653621</v>
+        <v>15.082743452</v>
       </c>
       <c r="Q7">
-        <v>26.56653621</v>
+        <v>26.482743452</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07917807629264156</v>
+        <v>0.07944083627251484</v>
       </c>
       <c r="T7">
-        <v>0.6113311891959504</v>
+        <v>0.616143730504823</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.20011221017454</v>
+        <v>31.00009350847878</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07687752609616395</v>
+        <v>0.07669992971431841</v>
       </c>
       <c r="C8">
-        <v>204.7651059635592</v>
+        <v>203.2382685003518</v>
       </c>
       <c r="D8">
-        <v>200.3571059635592</v>
+        <v>201.1122685003517</v>
       </c>
       <c r="E8">
-        <v>-106.908</v>
+        <v>-104.626</v>
       </c>
       <c r="F8">
-        <v>13.692</v>
+        <v>15.974</v>
       </c>
       <c r="G8">
         <v>18.1</v>
@@ -1943,28 +1943,28 @@
         <v>21.35</v>
       </c>
       <c r="M8">
-        <v>0.6887075999999999</v>
+        <v>0.8034921999999999</v>
       </c>
       <c r="N8">
-        <v>20.6612924</v>
+        <v>20.5465078</v>
       </c>
       <c r="O8">
-        <v>5.578548948000001</v>
+        <v>5.547557106</v>
       </c>
       <c r="P8">
-        <v>15.082743452</v>
+        <v>14.998950694</v>
       </c>
       <c r="Q8">
-        <v>26.482743452</v>
+        <v>26.398950694</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07944083627251484</v>
+        <v>0.07970924700464345</v>
       </c>
       <c r="T8">
-        <v>0.616143730504823</v>
+        <v>0.621059767325714</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.00009350847879</v>
+        <v>26.57150872155324</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0766999297143184</v>
+        <v>0.07652233333247287</v>
       </c>
       <c r="C9">
-        <v>203.2382685003518</v>
+        <v>201.717145114344</v>
       </c>
       <c r="D9">
-        <v>201.1122685003518</v>
+        <v>201.873145114344</v>
       </c>
       <c r="E9">
-        <v>-104.626</v>
+        <v>-102.344</v>
       </c>
       <c r="F9">
-        <v>15.974</v>
+        <v>18.256</v>
       </c>
       <c r="G9">
         <v>18.1</v>
@@ -2025,28 +2025,28 @@
         <v>21.35</v>
       </c>
       <c r="M9">
-        <v>0.8034922</v>
+        <v>0.9182768</v>
       </c>
       <c r="N9">
-        <v>20.5465078</v>
+        <v>20.4317232</v>
       </c>
       <c r="O9">
-        <v>5.547557106</v>
+        <v>5.516565264</v>
       </c>
       <c r="P9">
-        <v>14.998950694</v>
+        <v>14.915157936</v>
       </c>
       <c r="Q9">
-        <v>26.398950694</v>
+        <v>26.315157936</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07970924700464345</v>
+        <v>0.0799834927526879</v>
       </c>
       <c r="T9">
-        <v>0.621059767325714</v>
+        <v>0.6260826745122766</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.57150872155324</v>
+        <v>23.25007013135908</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07652233333247287</v>
+        <v>0.07634473695062734</v>
       </c>
       <c r="C10">
-        <v>201.717145114344</v>
+        <v>200.2018009067713</v>
       </c>
       <c r="D10">
-        <v>201.873145114344</v>
+        <v>202.6398009067713</v>
       </c>
       <c r="E10">
-        <v>-102.344</v>
+        <v>-100.062</v>
       </c>
       <c r="F10">
-        <v>18.256</v>
+        <v>20.538</v>
       </c>
       <c r="G10">
         <v>18.1</v>
@@ -2107,28 +2107,28 @@
         <v>21.35</v>
       </c>
       <c r="M10">
-        <v>0.9182768</v>
+        <v>1.0330614</v>
       </c>
       <c r="N10">
-        <v>20.4317232</v>
+        <v>20.3169386</v>
       </c>
       <c r="O10">
-        <v>5.516565264</v>
+        <v>5.485573422000001</v>
       </c>
       <c r="P10">
-        <v>14.915157936</v>
+        <v>14.831365178</v>
       </c>
       <c r="Q10">
-        <v>26.315157936</v>
+        <v>26.231365178</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0799834927526879</v>
+        <v>0.08026376587981025</v>
       </c>
       <c r="T10">
-        <v>0.6260826745122766</v>
+        <v>0.6312159752633792</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.25007013135908</v>
+        <v>20.66672900565252</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07634473695062734</v>
+        <v>0.07616714056878179</v>
       </c>
       <c r="C11">
-        <v>200.2018009067713</v>
+        <v>198.6923019715819</v>
       </c>
       <c r="D11">
-        <v>202.6398009067713</v>
+        <v>203.4123019715819</v>
       </c>
       <c r="E11">
-        <v>-100.062</v>
+        <v>-97.78</v>
       </c>
       <c r="F11">
-        <v>20.538</v>
+        <v>22.82</v>
       </c>
       <c r="G11">
         <v>18.1</v>
@@ -2189,28 +2189,28 @@
         <v>21.35</v>
       </c>
       <c r="M11">
-        <v>1.0330614</v>
+        <v>1.147846</v>
       </c>
       <c r="N11">
-        <v>20.3169386</v>
+        <v>20.202154</v>
       </c>
       <c r="O11">
-        <v>5.485573422000001</v>
+        <v>5.45458158</v>
       </c>
       <c r="P11">
-        <v>14.831365178</v>
+        <v>14.74757242</v>
       </c>
       <c r="Q11">
-        <v>26.231365178</v>
+        <v>26.14757242</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08026376587981025</v>
+        <v>0.08055026729864642</v>
       </c>
       <c r="T11">
-        <v>0.6312159752633792</v>
+        <v>0.6364633493645062</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.66672900565252</v>
+        <v>18.60005610508727</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07616714056878179</v>
+        <v>0.07598954418693624</v>
       </c>
       <c r="C12">
-        <v>198.6923019715819</v>
+        <v>197.188715414431</v>
       </c>
       <c r="D12">
-        <v>203.4123019715819</v>
+        <v>204.190715414431</v>
       </c>
       <c r="E12">
-        <v>-97.78</v>
+        <v>-95.49799999999999</v>
       </c>
       <c r="F12">
-        <v>22.82</v>
+        <v>25.102</v>
       </c>
       <c r="G12">
         <v>18.1</v>
@@ -2271,28 +2271,28 @@
         <v>21.35</v>
       </c>
       <c r="M12">
-        <v>1.147846</v>
+        <v>1.2626306</v>
       </c>
       <c r="N12">
-        <v>20.202154</v>
+        <v>20.0873694</v>
       </c>
       <c r="O12">
-        <v>5.45458158</v>
+        <v>5.423589738</v>
       </c>
       <c r="P12">
-        <v>14.74757242</v>
+        <v>14.663779662</v>
       </c>
       <c r="Q12">
-        <v>26.14757242</v>
+        <v>26.063779662</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08055026729864642</v>
+        <v>0.08084320695161376</v>
       </c>
       <c r="T12">
-        <v>0.6364633493645062</v>
+        <v>0.6418286419847596</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.60005610508727</v>
+        <v>16.9091419137157</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07598954418693624</v>
+        <v>0.07581194780509072</v>
       </c>
       <c r="C13">
-        <v>197.188715414431</v>
+        <v>195.691109372113</v>
       </c>
       <c r="D13">
-        <v>204.190715414431</v>
+        <v>204.975109372113</v>
       </c>
       <c r="E13">
-        <v>-95.49799999999999</v>
+        <v>-93.21599999999999</v>
       </c>
       <c r="F13">
-        <v>25.102</v>
+        <v>27.384</v>
       </c>
       <c r="G13">
         <v>18.1</v>
@@ -2353,28 +2353,28 @@
         <v>21.35</v>
       </c>
       <c r="M13">
-        <v>1.2626306</v>
+        <v>1.3774152</v>
       </c>
       <c r="N13">
-        <v>20.0873694</v>
+        <v>19.9725848</v>
       </c>
       <c r="O13">
-        <v>5.423589738</v>
+        <v>5.392597896000001</v>
       </c>
       <c r="P13">
-        <v>14.663779662</v>
+        <v>14.579986904</v>
       </c>
       <c r="Q13">
-        <v>26.063779662</v>
+        <v>25.979986904</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08084320695161376</v>
+        <v>0.08114280432396673</v>
       </c>
       <c r="T13">
-        <v>0.6418286419847596</v>
+        <v>0.6473158730736553</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.9091419137157</v>
+        <v>15.50004675423939</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07581194780509072</v>
+        <v>0.07563435142324518</v>
       </c>
       <c r="C14">
-        <v>195.691109372113</v>
+        <v>194.1995530324438</v>
       </c>
       <c r="D14">
-        <v>204.975109372113</v>
+        <v>205.7655530324438</v>
       </c>
       <c r="E14">
-        <v>-93.21599999999999</v>
+        <v>-90.934</v>
       </c>
       <c r="F14">
-        <v>27.384</v>
+        <v>29.666</v>
       </c>
       <c r="G14">
         <v>18.1</v>
@@ -2435,28 +2435,28 @@
         <v>21.35</v>
       </c>
       <c r="M14">
-        <v>1.3774152</v>
+        <v>1.4921998</v>
       </c>
       <c r="N14">
-        <v>19.9725848</v>
+        <v>19.8578002</v>
       </c>
       <c r="O14">
-        <v>5.392597896000001</v>
+        <v>5.361606054</v>
       </c>
       <c r="P14">
-        <v>14.579986904</v>
+        <v>14.496194146</v>
       </c>
       <c r="Q14">
-        <v>25.979986904</v>
+        <v>25.896194146</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08114280432396673</v>
+        <v>0.08144928899223583</v>
       </c>
       <c r="T14">
-        <v>0.6473158730736553</v>
+        <v>0.6529292474059737</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.50004675423939</v>
+        <v>14.30773546545175</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07563435142324518</v>
+        <v>0.07545675504139963</v>
       </c>
       <c r="C15">
-        <v>194.1995530324438</v>
+        <v>192.7141166546041</v>
       </c>
       <c r="D15">
-        <v>205.7655530324438</v>
+        <v>206.5621166546042</v>
       </c>
       <c r="E15">
-        <v>-90.934</v>
+        <v>-88.65199999999999</v>
       </c>
       <c r="F15">
-        <v>29.666</v>
+        <v>31.948</v>
       </c>
       <c r="G15">
         <v>18.1</v>
@@ -2517,28 +2517,28 @@
         <v>21.35</v>
       </c>
       <c r="M15">
-        <v>1.4921998</v>
+        <v>1.6069844</v>
       </c>
       <c r="N15">
-        <v>19.8578002</v>
+        <v>19.7430156</v>
       </c>
       <c r="O15">
-        <v>5.361606054</v>
+        <v>5.330614212</v>
       </c>
       <c r="P15">
-        <v>14.496194146</v>
+        <v>14.412401388</v>
       </c>
       <c r="Q15">
-        <v>25.896194146</v>
+        <v>25.812401388</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08144928899223583</v>
+        <v>0.0817629012109298</v>
       </c>
       <c r="T15">
-        <v>0.6529292474059737</v>
+        <v>0.6586731653274159</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.30773546545175</v>
+        <v>13.28575436077662</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07545675504139963</v>
+        <v>0.0754434086595541</v>
       </c>
       <c r="C16">
-        <v>192.7141166546041</v>
+        <v>190.4922276983697</v>
       </c>
       <c r="D16">
-        <v>206.5621166546042</v>
+        <v>206.6222276983697</v>
       </c>
       <c r="E16">
-        <v>-88.65199999999999</v>
+        <v>-86.36999999999999</v>
       </c>
       <c r="F16">
-        <v>31.948</v>
+        <v>34.23</v>
       </c>
       <c r="G16">
         <v>18.1</v>
@@ -2599,45 +2599,45 @@
         <v>21.35</v>
       </c>
       <c r="M16">
-        <v>1.6069844</v>
+        <v>1.773114</v>
       </c>
       <c r="N16">
-        <v>19.7430156</v>
+        <v>19.576886</v>
       </c>
       <c r="O16">
-        <v>5.330614212</v>
+        <v>5.285759220000001</v>
       </c>
       <c r="P16">
-        <v>14.412401388</v>
+        <v>14.29112678</v>
       </c>
       <c r="Q16">
-        <v>25.812401388</v>
+        <v>25.69112678</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0817629012109298</v>
+        <v>0.08208389254065188</v>
       </c>
       <c r="T16">
-        <v>0.6586731653274159</v>
+        <v>0.6645522342587744</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.27</v>
       </c>
       <c r="W16">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.28575436077662</v>
+        <v>12.04096296120836</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0754434086595541</v>
+        <v>0.07527676227770855</v>
       </c>
       <c r="C17">
-        <v>190.4922276983697</v>
+        <v>188.9637461620789</v>
       </c>
       <c r="D17">
-        <v>206.6222276983697</v>
+        <v>207.3757461620789</v>
       </c>
       <c r="E17">
-        <v>-86.37</v>
+        <v>-84.08799999999999</v>
       </c>
       <c r="F17">
-        <v>34.23</v>
+        <v>36.512</v>
       </c>
       <c r="G17">
         <v>18.1</v>
@@ -2681,28 +2681,28 @@
         <v>21.35</v>
       </c>
       <c r="M17">
-        <v>1.773114</v>
+        <v>1.8913216</v>
       </c>
       <c r="N17">
-        <v>19.576886</v>
+        <v>19.4586784</v>
       </c>
       <c r="O17">
-        <v>5.285759220000001</v>
+        <v>5.253843168</v>
       </c>
       <c r="P17">
-        <v>14.29112678</v>
+        <v>14.204835232</v>
       </c>
       <c r="Q17">
-        <v>25.69112678</v>
+        <v>25.604835232</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08208389254065188</v>
+        <v>0.08241252652108161</v>
       </c>
       <c r="T17">
-        <v>0.6645522342587744</v>
+        <v>0.6705712810218318</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.04096296120836</v>
+        <v>11.28840277613284</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07527676227770855</v>
+        <v>0.075110115895863</v>
       </c>
       <c r="C18">
-        <v>188.9637461620789</v>
+        <v>187.4407806663488</v>
       </c>
       <c r="D18">
-        <v>207.3757461620789</v>
+        <v>208.1347806663488</v>
       </c>
       <c r="E18">
-        <v>-84.08799999999999</v>
+        <v>-81.80599999999998</v>
       </c>
       <c r="F18">
-        <v>36.512</v>
+        <v>38.794</v>
       </c>
       <c r="G18">
         <v>18.1</v>
@@ -2763,28 +2763,28 @@
         <v>21.35</v>
       </c>
       <c r="M18">
-        <v>1.8913216</v>
+        <v>2.0095292</v>
       </c>
       <c r="N18">
-        <v>19.4586784</v>
+        <v>19.3404708</v>
       </c>
       <c r="O18">
-        <v>5.253843168</v>
+        <v>5.221927116000001</v>
       </c>
       <c r="P18">
-        <v>14.204835232</v>
+        <v>14.118543684</v>
       </c>
       <c r="Q18">
-        <v>25.604835232</v>
+        <v>25.518543684</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08241252652108161</v>
+        <v>0.08274907939260603</v>
       </c>
       <c r="T18">
-        <v>0.6705712810218318</v>
+        <v>0.6767353650562883</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.28840277613284</v>
+        <v>10.62437908341914</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.075110115895863</v>
+        <v>0.07494346951401745</v>
       </c>
       <c r="C19">
-        <v>187.4407806663488</v>
+        <v>185.923392002948</v>
       </c>
       <c r="D19">
-        <v>208.1347806663488</v>
+        <v>208.899392002948</v>
       </c>
       <c r="E19">
-        <v>-81.80599999999998</v>
+        <v>-79.524</v>
       </c>
       <c r="F19">
-        <v>38.794</v>
+        <v>41.076</v>
       </c>
       <c r="G19">
         <v>18.1</v>
@@ -2845,28 +2845,28 @@
         <v>21.35</v>
       </c>
       <c r="M19">
-        <v>2.0095292</v>
+        <v>2.1277368</v>
       </c>
       <c r="N19">
-        <v>19.3404708</v>
+        <v>19.2222632</v>
       </c>
       <c r="O19">
-        <v>5.221927116000001</v>
+        <v>5.190011064</v>
       </c>
       <c r="P19">
-        <v>14.118543684</v>
+        <v>14.032252136</v>
       </c>
       <c r="Q19">
-        <v>25.518543684</v>
+        <v>25.432252136</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08274907939260603</v>
+        <v>0.083093840870753</v>
       </c>
       <c r="T19">
-        <v>0.6767353650562883</v>
+        <v>0.6830497926037802</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.62437908341914</v>
+        <v>10.03413580100697</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07494346951401747</v>
+        <v>0.07501261313217193</v>
       </c>
       <c r="C20">
-        <v>185.9233920029479</v>
+        <v>183.3234645736375</v>
       </c>
       <c r="D20">
-        <v>208.8993920029479</v>
+        <v>208.5814645736375</v>
       </c>
       <c r="E20">
-        <v>-79.524</v>
+        <v>-77.24199999999999</v>
       </c>
       <c r="F20">
-        <v>41.07599999999999</v>
+        <v>43.358</v>
       </c>
       <c r="G20">
         <v>18.1</v>
@@ -2927,45 +2927,45 @@
         <v>21.35</v>
       </c>
       <c r="M20">
-        <v>2.1277368</v>
+        <v>2.319653</v>
       </c>
       <c r="N20">
-        <v>19.2222632</v>
+        <v>19.030347</v>
       </c>
       <c r="O20">
-        <v>5.190011064</v>
+        <v>5.138193690000001</v>
       </c>
       <c r="P20">
-        <v>14.032252136</v>
+        <v>13.89215331</v>
       </c>
       <c r="Q20">
-        <v>25.432252136</v>
+        <v>25.29215331</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.083093840870753</v>
+        <v>0.08344711497799004</v>
       </c>
       <c r="T20">
-        <v>0.6830497926037802</v>
+        <v>0.6895201319425683</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.27</v>
       </c>
       <c r="W20">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.03413580100697</v>
+        <v>9.203962834096309</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07501261313217193</v>
+        <v>0.07485837675032639</v>
       </c>
       <c r="C21">
-        <v>183.3234645736375</v>
+        <v>181.7519875919737</v>
       </c>
       <c r="D21">
-        <v>208.5814645736375</v>
+        <v>209.2919875919737</v>
       </c>
       <c r="E21">
-        <v>-77.24199999999999</v>
+        <v>-74.95999999999999</v>
       </c>
       <c r="F21">
-        <v>43.358</v>
+        <v>45.64</v>
       </c>
       <c r="G21">
         <v>18.1</v>
@@ -3009,28 +3009,28 @@
         <v>21.35</v>
       </c>
       <c r="M21">
-        <v>2.319653</v>
+        <v>2.44174</v>
       </c>
       <c r="N21">
-        <v>19.030347</v>
+        <v>18.90826</v>
       </c>
       <c r="O21">
-        <v>5.138193690000001</v>
+        <v>5.105230200000001</v>
       </c>
       <c r="P21">
-        <v>13.89215331</v>
+        <v>13.8030298</v>
       </c>
       <c r="Q21">
-        <v>25.29215331</v>
+        <v>25.2030298</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08344711497799004</v>
+        <v>0.08380922093790799</v>
       </c>
       <c r="T21">
-        <v>0.6895201319425683</v>
+        <v>0.696152229764826</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.203962834096309</v>
+        <v>8.743764692391494</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07485837675032639</v>
+        <v>0.07470414036848085</v>
       </c>
       <c r="C22">
-        <v>181.7519875919737</v>
+        <v>180.1853678833448</v>
       </c>
       <c r="D22">
-        <v>209.2919875919737</v>
+        <v>210.0073678833448</v>
       </c>
       <c r="E22">
-        <v>-74.95999999999999</v>
+        <v>-72.678</v>
       </c>
       <c r="F22">
-        <v>45.64</v>
+        <v>47.922</v>
       </c>
       <c r="G22">
         <v>18.1</v>
@@ -3091,28 +3091,28 @@
         <v>21.35</v>
       </c>
       <c r="M22">
-        <v>2.44174</v>
+        <v>2.563827</v>
       </c>
       <c r="N22">
-        <v>18.90826</v>
+        <v>18.786173</v>
       </c>
       <c r="O22">
-        <v>5.105230200000001</v>
+        <v>5.072266710000001</v>
       </c>
       <c r="P22">
-        <v>13.8030298</v>
+        <v>13.71390629</v>
       </c>
       <c r="Q22">
-        <v>25.2030298</v>
+        <v>25.11390629</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08380922093790799</v>
+        <v>0.08418049413731751</v>
       </c>
       <c r="T22">
-        <v>0.696152229764826</v>
+        <v>0.7029522287977739</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.743764692391494</v>
+        <v>8.327394945134753</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07470414036848085</v>
+        <v>0.0745499039866353</v>
       </c>
       <c r="C23">
-        <v>180.1853678833448</v>
+        <v>178.6236554264725</v>
       </c>
       <c r="D23">
-        <v>210.0073678833448</v>
+        <v>210.7276554264725</v>
       </c>
       <c r="E23">
-        <v>-72.678</v>
+        <v>-70.39599999999999</v>
       </c>
       <c r="F23">
-        <v>47.922</v>
+        <v>50.204</v>
       </c>
       <c r="G23">
         <v>18.1</v>
@@ -3173,28 +3173,28 @@
         <v>21.35</v>
       </c>
       <c r="M23">
-        <v>2.563827</v>
+        <v>2.685914</v>
       </c>
       <c r="N23">
-        <v>18.786173</v>
+        <v>18.664086</v>
       </c>
       <c r="O23">
-        <v>5.072266710000001</v>
+        <v>5.039303220000001</v>
       </c>
       <c r="P23">
-        <v>13.71390629</v>
+        <v>13.62478278</v>
       </c>
       <c r="Q23">
-        <v>25.11390629</v>
+        <v>25.02478278</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08418049413731751</v>
+        <v>0.08456128716235295</v>
       </c>
       <c r="T23">
-        <v>0.7029522287977739</v>
+        <v>0.7099265867802844</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.327394945134754</v>
+        <v>7.948876993083174</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0745499039866353</v>
+        <v>0.07452998760478975</v>
       </c>
       <c r="C24">
-        <v>178.6236554264725</v>
+        <v>176.4350257599099</v>
       </c>
       <c r="D24">
-        <v>210.7276554264725</v>
+        <v>210.8210257599099</v>
       </c>
       <c r="E24">
-        <v>-70.39599999999999</v>
+        <v>-68.114</v>
       </c>
       <c r="F24">
-        <v>50.204</v>
+        <v>52.486</v>
       </c>
       <c r="G24">
         <v>18.1</v>
@@ -3255,45 +3255,45 @@
         <v>21.35</v>
       </c>
       <c r="M24">
-        <v>2.685914</v>
+        <v>2.8499898</v>
       </c>
       <c r="N24">
-        <v>18.664086</v>
+        <v>18.5000102</v>
       </c>
       <c r="O24">
-        <v>5.039303220000001</v>
+        <v>4.995002754000001</v>
       </c>
       <c r="P24">
-        <v>13.62478278</v>
+        <v>13.505007446</v>
       </c>
       <c r="Q24">
-        <v>25.02478278</v>
+        <v>24.905007446</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08456128716235295</v>
+        <v>0.08495197091531137</v>
       </c>
       <c r="T24">
-        <v>0.7099265867802844</v>
+        <v>0.7170820969181849</v>
       </c>
       <c r="U24">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.27</v>
       </c>
       <c r="W24">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.948876993083174</v>
+        <v>7.491254880982382</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07452998760478975</v>
+        <v>0.07438159122294423</v>
       </c>
       <c r="C25">
-        <v>176.4350257599099</v>
+        <v>174.8513390756046</v>
       </c>
       <c r="D25">
-        <v>210.8210257599099</v>
+        <v>211.5193390756046</v>
       </c>
       <c r="E25">
-        <v>-68.114</v>
+        <v>-65.83199999999999</v>
       </c>
       <c r="F25">
-        <v>52.486</v>
+        <v>54.768</v>
       </c>
       <c r="G25">
         <v>18.1</v>
@@ -3337,28 +3337,28 @@
         <v>21.35</v>
       </c>
       <c r="M25">
-        <v>2.8499898</v>
+        <v>2.9739024</v>
       </c>
       <c r="N25">
-        <v>18.5000102</v>
+        <v>18.3760976</v>
       </c>
       <c r="O25">
-        <v>4.995002754000001</v>
+        <v>4.961546352000001</v>
       </c>
       <c r="P25">
-        <v>13.505007446</v>
+        <v>13.414551248</v>
       </c>
       <c r="Q25">
-        <v>24.905007446</v>
+        <v>24.814551248</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08495197091531137</v>
+        <v>0.08535293581966345</v>
       </c>
       <c r="T25">
-        <v>0.7170820969181849</v>
+        <v>0.7244259099544512</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.491254880982382</v>
+        <v>7.179119260941449</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07438159122294423</v>
+        <v>0.07423319484109868</v>
       </c>
       <c r="C26">
-        <v>174.8513390756046</v>
+        <v>173.2722938837036</v>
       </c>
       <c r="D26">
-        <v>211.5193390756046</v>
+        <v>212.2222938837036</v>
       </c>
       <c r="E26">
-        <v>-65.83199999999999</v>
+        <v>-63.55</v>
       </c>
       <c r="F26">
-        <v>54.76799999999999</v>
+        <v>57.05</v>
       </c>
       <c r="G26">
         <v>18.1</v>
@@ -3419,28 +3419,28 @@
         <v>21.35</v>
       </c>
       <c r="M26">
-        <v>2.9739024</v>
+        <v>3.097815</v>
       </c>
       <c r="N26">
-        <v>18.3760976</v>
+        <v>18.252185</v>
       </c>
       <c r="O26">
-        <v>4.961546352000001</v>
+        <v>4.92808995</v>
       </c>
       <c r="P26">
-        <v>13.414551248</v>
+        <v>13.32409505</v>
       </c>
       <c r="Q26">
-        <v>24.814551248</v>
+        <v>24.72409505</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08535293581966345</v>
+        <v>0.08576459312146491</v>
       </c>
       <c r="T26">
-        <v>0.7244259099544512</v>
+        <v>0.7319655580050179</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.17911926094145</v>
+        <v>6.891954490503791</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07423319484109868</v>
+        <v>0.07408479845925314</v>
       </c>
       <c r="C27">
-        <v>173.2722938837036</v>
+        <v>171.6979366145552</v>
       </c>
       <c r="D27">
-        <v>212.2222938837036</v>
+        <v>212.9299366145552</v>
       </c>
       <c r="E27">
-        <v>-63.55</v>
+        <v>-61.26799999999999</v>
       </c>
       <c r="F27">
-        <v>57.05</v>
+        <v>59.332</v>
       </c>
       <c r="G27">
         <v>18.1</v>
@@ -3501,28 +3501,28 @@
         <v>21.35</v>
       </c>
       <c r="M27">
-        <v>3.097815</v>
+        <v>3.2217276</v>
       </c>
       <c r="N27">
-        <v>18.252185</v>
+        <v>18.1282724</v>
       </c>
       <c r="O27">
-        <v>4.92808995</v>
+        <v>4.894633548000001</v>
       </c>
       <c r="P27">
-        <v>13.32409505</v>
+        <v>13.233638852</v>
       </c>
       <c r="Q27">
-        <v>24.72409505</v>
+        <v>24.633638852</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08576459312146491</v>
+        <v>0.08618737629628803</v>
       </c>
       <c r="T27">
-        <v>0.7319655580050179</v>
+        <v>0.7397089803272215</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.891954490503791</v>
+        <v>6.626879317792106</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07408479845925314</v>
+        <v>0.07393640207740759</v>
       </c>
       <c r="C28">
-        <v>171.6979366145552</v>
+        <v>170.1283143198571</v>
       </c>
       <c r="D28">
-        <v>212.9299366145552</v>
+        <v>213.6423143198571</v>
       </c>
       <c r="E28">
-        <v>-61.26799999999999</v>
+        <v>-58.98599999999999</v>
       </c>
       <c r="F28">
-        <v>59.332</v>
+        <v>61.614</v>
       </c>
       <c r="G28">
         <v>18.1</v>
@@ -3583,28 +3583,28 @@
         <v>21.35</v>
       </c>
       <c r="M28">
-        <v>3.2217276</v>
+        <v>3.345640200000001</v>
       </c>
       <c r="N28">
-        <v>18.1282724</v>
+        <v>18.0043598</v>
       </c>
       <c r="O28">
-        <v>4.894633548000001</v>
+        <v>4.861177146</v>
       </c>
       <c r="P28">
-        <v>13.233638852</v>
+        <v>13.143182654</v>
       </c>
       <c r="Q28">
-        <v>24.633638852</v>
+        <v>24.543182654</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08618737629628803</v>
+        <v>0.08662174257179123</v>
       </c>
       <c r="T28">
-        <v>0.7397089803272215</v>
+        <v>0.7476645512061979</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.626879317792106</v>
+        <v>6.381439343059064</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07393640207740759</v>
+        <v>0.07378800569556206</v>
       </c>
       <c r="C29">
-        <v>170.1283143198571</v>
+        <v>168.5634746830843</v>
       </c>
       <c r="D29">
-        <v>213.6423143198571</v>
+        <v>214.3594746830844</v>
       </c>
       <c r="E29">
-        <v>-58.98599999999999</v>
+        <v>-56.70399999999999</v>
       </c>
       <c r="F29">
-        <v>61.614</v>
+        <v>63.896</v>
       </c>
       <c r="G29">
         <v>18.1</v>
@@ -3665,28 +3665,28 @@
         <v>21.35</v>
       </c>
       <c r="M29">
-        <v>3.345640200000001</v>
+        <v>3.4695528</v>
       </c>
       <c r="N29">
-        <v>18.0043598</v>
+        <v>17.8804472</v>
       </c>
       <c r="O29">
-        <v>4.861177146</v>
+        <v>4.827720744000001</v>
       </c>
       <c r="P29">
-        <v>13.143182654</v>
+        <v>13.052726456</v>
       </c>
       <c r="Q29">
-        <v>24.543182654</v>
+        <v>24.452726456</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08662174257179123</v>
+        <v>0.08706817457716953</v>
       </c>
       <c r="T29">
-        <v>0.7476645512061979</v>
+        <v>0.7558411101651459</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.381439343059064</v>
+        <v>6.153530795092671</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07378800569556206</v>
+        <v>0.07385130931371651</v>
       </c>
       <c r="C30">
-        <v>168.5634746830843</v>
+        <v>165.9749570542582</v>
       </c>
       <c r="D30">
-        <v>214.3594746830844</v>
+        <v>214.0529570542582</v>
       </c>
       <c r="E30">
-        <v>-56.70399999999999</v>
+        <v>-54.42199999999998</v>
       </c>
       <c r="F30">
-        <v>63.896</v>
+        <v>66.17800000000001</v>
       </c>
       <c r="G30">
         <v>18.1</v>
@@ -3747,45 +3747,45 @@
         <v>21.35</v>
       </c>
       <c r="M30">
-        <v>3.4695528</v>
+        <v>3.659643400000001</v>
       </c>
       <c r="N30">
-        <v>17.8804472</v>
+        <v>17.6903566</v>
       </c>
       <c r="O30">
-        <v>4.827720744000001</v>
+        <v>4.776396282</v>
       </c>
       <c r="P30">
-        <v>13.052726456</v>
+        <v>12.913960318</v>
       </c>
       <c r="Q30">
-        <v>24.452726456</v>
+        <v>24.313960318</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08706817457716953</v>
+        <v>0.08752718213199509</v>
       </c>
       <c r="T30">
-        <v>0.7558411101651459</v>
+        <v>0.7642479947285712</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.27</v>
       </c>
       <c r="W30">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.153530795092671</v>
+        <v>5.833901740262452</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07385130931371651</v>
+        <v>0.07371021293187097</v>
       </c>
       <c r="C31">
-        <v>165.9749570542582</v>
+        <v>164.3773534498433</v>
       </c>
       <c r="D31">
-        <v>214.0529570542582</v>
+        <v>214.7373534498433</v>
       </c>
       <c r="E31">
-        <v>-54.422</v>
+        <v>-52.14</v>
       </c>
       <c r="F31">
-        <v>66.178</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="G31">
         <v>18.1</v>
@@ -3829,28 +3829,28 @@
         <v>21.35</v>
       </c>
       <c r="M31">
-        <v>3.6596434</v>
+        <v>3.785838</v>
       </c>
       <c r="N31">
-        <v>17.6903566</v>
+        <v>17.564162</v>
       </c>
       <c r="O31">
-        <v>4.776396282</v>
+        <v>4.742323740000002</v>
       </c>
       <c r="P31">
-        <v>12.913960318</v>
+        <v>12.82183826</v>
       </c>
       <c r="Q31">
-        <v>24.313960318</v>
+        <v>24.22183826</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08752718213199509</v>
+        <v>0.08799930418838711</v>
       </c>
       <c r="T31">
-        <v>0.7642479947285712</v>
+        <v>0.7728950759938087</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.833901740262453</v>
+        <v>5.639438348920373</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07371021293187097</v>
+        <v>0.07356911655002543</v>
       </c>
       <c r="C32">
-        <v>164.3773534498433</v>
+        <v>162.7841403556783</v>
       </c>
       <c r="D32">
-        <v>214.7373534498433</v>
+        <v>215.4261403556783</v>
       </c>
       <c r="E32">
-        <v>-52.14</v>
+        <v>-49.858</v>
       </c>
       <c r="F32">
-        <v>68.45999999999999</v>
+        <v>70.74199999999999</v>
       </c>
       <c r="G32">
         <v>18.1</v>
@@ -3911,28 +3911,28 @@
         <v>21.35</v>
       </c>
       <c r="M32">
-        <v>3.785838</v>
+        <v>3.912032599999999</v>
       </c>
       <c r="N32">
-        <v>17.564162</v>
+        <v>17.4379674</v>
       </c>
       <c r="O32">
-        <v>4.742323740000002</v>
+        <v>4.708251198000001</v>
       </c>
       <c r="P32">
-        <v>12.82183826</v>
+        <v>12.729716202</v>
       </c>
       <c r="Q32">
-        <v>24.22183826</v>
+        <v>24.129716202</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08799930418838711</v>
+        <v>0.08848511094206585</v>
       </c>
       <c r="T32">
-        <v>0.7728950759938087</v>
+        <v>0.7817927972957197</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.639438348920373</v>
+        <v>5.457520982826167</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07356911655002543</v>
+        <v>0.0734280201681799</v>
       </c>
       <c r="C33">
-        <v>162.7841403556783</v>
+        <v>161.1953601564333</v>
       </c>
       <c r="D33">
-        <v>215.4261403556783</v>
+        <v>216.1193601564333</v>
       </c>
       <c r="E33">
-        <v>-49.858</v>
+        <v>-47.57599999999999</v>
       </c>
       <c r="F33">
-        <v>70.74199999999999</v>
+        <v>73.024</v>
       </c>
       <c r="G33">
         <v>18.1</v>
@@ -3993,28 +3993,28 @@
         <v>21.35</v>
       </c>
       <c r="M33">
-        <v>3.912032599999999</v>
+        <v>4.038227200000001</v>
       </c>
       <c r="N33">
-        <v>17.4379674</v>
+        <v>17.3117728</v>
       </c>
       <c r="O33">
-        <v>4.708251198000001</v>
+        <v>4.674178656</v>
       </c>
       <c r="P33">
-        <v>12.729716202</v>
+        <v>12.637594144</v>
       </c>
       <c r="Q33">
-        <v>24.129716202</v>
+        <v>24.037594144</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08848511094206585</v>
+        <v>0.08898520612967632</v>
       </c>
       <c r="T33">
-        <v>0.7817927972957197</v>
+        <v>0.7909522162829811</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.457520982826167</v>
+        <v>5.286973452112847</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0734280201681799</v>
+        <v>0.07328692378633436</v>
       </c>
       <c r="C34">
-        <v>161.1953601564333</v>
+        <v>159.6110557840986</v>
       </c>
       <c r="D34">
-        <v>216.1193601564333</v>
+        <v>216.8170557840986</v>
       </c>
       <c r="E34">
-        <v>-47.57599999999999</v>
+        <v>-45.294</v>
       </c>
       <c r="F34">
-        <v>73.024</v>
+        <v>75.306</v>
       </c>
       <c r="G34">
         <v>18.1</v>
@@ -4075,28 +4075,28 @@
         <v>21.35</v>
       </c>
       <c r="M34">
-        <v>4.038227200000001</v>
+        <v>4.1644218</v>
       </c>
       <c r="N34">
-        <v>17.3117728</v>
+        <v>17.1855782</v>
       </c>
       <c r="O34">
-        <v>4.674178656</v>
+        <v>4.640106114000001</v>
       </c>
       <c r="P34">
-        <v>12.637594144</v>
+        <v>12.545472086</v>
       </c>
       <c r="Q34">
-        <v>24.037594144</v>
+        <v>23.945472086</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08898520612967632</v>
+        <v>0.08950022953184233</v>
       </c>
       <c r="T34">
-        <v>0.7909522162829811</v>
+        <v>0.8003850507623995</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.286973452112847</v>
+        <v>5.126762135382156</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07328692378633436</v>
+        <v>0.07314582740448881</v>
       </c>
       <c r="C35">
-        <v>159.6110557840986</v>
+        <v>158.031270726847</v>
       </c>
       <c r="D35">
-        <v>216.8170557840986</v>
+        <v>217.519270726847</v>
       </c>
       <c r="E35">
-        <v>-45.294</v>
+        <v>-43.01199999999999</v>
       </c>
       <c r="F35">
-        <v>75.306</v>
+        <v>77.58800000000001</v>
       </c>
       <c r="G35">
         <v>18.1</v>
@@ -4157,28 +4157,28 @@
         <v>21.35</v>
       </c>
       <c r="M35">
-        <v>4.1644218</v>
+        <v>4.2906164</v>
       </c>
       <c r="N35">
-        <v>17.1855782</v>
+        <v>17.0593836</v>
       </c>
       <c r="O35">
-        <v>4.640106114000001</v>
+        <v>4.606033572</v>
       </c>
       <c r="P35">
-        <v>12.545472086</v>
+        <v>12.453350028</v>
       </c>
       <c r="Q35">
-        <v>23.945472086</v>
+        <v>23.853350028</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08950022953184233</v>
+        <v>0.09003085970377094</v>
       </c>
       <c r="T35">
-        <v>0.8003850507623995</v>
+        <v>0.8101037287108911</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.126762135382156</v>
+        <v>4.975975013753269</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07314582740448881</v>
+        <v>0.07300473102264327</v>
       </c>
       <c r="C36">
-        <v>158.031270726847</v>
+        <v>156.4560490380703</v>
       </c>
       <c r="D36">
-        <v>217.519270726847</v>
+        <v>218.2260490380703</v>
       </c>
       <c r="E36">
-        <v>-43.01199999999999</v>
+        <v>-40.72999999999999</v>
       </c>
       <c r="F36">
-        <v>77.58800000000001</v>
+        <v>79.87</v>
       </c>
       <c r="G36">
         <v>18.1</v>
@@ -4239,28 +4239,28 @@
         <v>21.35</v>
       </c>
       <c r="M36">
-        <v>4.2906164</v>
+        <v>4.416811</v>
       </c>
       <c r="N36">
-        <v>17.0593836</v>
+        <v>16.933189</v>
       </c>
       <c r="O36">
-        <v>4.606033572</v>
+        <v>4.571961030000001</v>
       </c>
       <c r="P36">
-        <v>12.453350028</v>
+        <v>12.36122797</v>
       </c>
       <c r="Q36">
-        <v>23.853350028</v>
+        <v>23.76122797</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09003085970377094</v>
+        <v>0.09057781695791273</v>
       </c>
       <c r="T36">
-        <v>0.8101037287108911</v>
+        <v>0.8201214429039518</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.975975013753269</v>
+        <v>4.833804299074604</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07300473102264327</v>
+        <v>0.07286363464079773</v>
       </c>
       <c r="C37">
-        <v>156.4560490380703</v>
+        <v>154.8854353455915</v>
       </c>
       <c r="D37">
-        <v>218.2260490380703</v>
+        <v>218.9374353455916</v>
       </c>
       <c r="E37">
-        <v>-40.72999999999999</v>
+        <v>-38.44799999999999</v>
       </c>
       <c r="F37">
-        <v>79.87</v>
+        <v>82.152</v>
       </c>
       <c r="G37">
         <v>18.1</v>
@@ -4321,28 +4321,28 @@
         <v>21.35</v>
       </c>
       <c r="M37">
-        <v>4.416811</v>
+        <v>4.5430056</v>
       </c>
       <c r="N37">
-        <v>16.933189</v>
+        <v>16.8069944</v>
       </c>
       <c r="O37">
-        <v>4.571961030000001</v>
+        <v>4.537888488</v>
       </c>
       <c r="P37">
-        <v>12.36122797</v>
+        <v>12.269105912</v>
       </c>
       <c r="Q37">
-        <v>23.76122797</v>
+        <v>23.669105912</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09057781695791273</v>
+        <v>0.09114186662624646</v>
       </c>
       <c r="T37">
-        <v>0.8201214429039518</v>
+        <v>0.8304522106655456</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.833804299074604</v>
+        <v>4.699531957433643</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07286363464079773</v>
+        <v>0.0727225382589522</v>
       </c>
       <c r="C38">
-        <v>154.8854353455916</v>
+        <v>153.3194748610591</v>
       </c>
       <c r="D38">
-        <v>218.9374353455916</v>
+        <v>219.6534748610591</v>
       </c>
       <c r="E38">
-        <v>-38.44800000000001</v>
+        <v>-36.166</v>
       </c>
       <c r="F38">
-        <v>82.15199999999999</v>
+        <v>84.434</v>
       </c>
       <c r="G38">
         <v>18.1</v>
@@ -4403,28 +4403,28 @@
         <v>21.35</v>
       </c>
       <c r="M38">
-        <v>4.5430056</v>
+        <v>4.6692002</v>
       </c>
       <c r="N38">
-        <v>16.8069944</v>
+        <v>16.6807998</v>
       </c>
       <c r="O38">
-        <v>4.537888488</v>
+        <v>4.503815946000001</v>
       </c>
       <c r="P38">
-        <v>12.269105912</v>
+        <v>12.176983854</v>
       </c>
       <c r="Q38">
-        <v>23.669105912</v>
+        <v>23.576983854</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09114186662624646</v>
+        <v>0.09172382263325746</v>
       </c>
       <c r="T38">
-        <v>0.8304522106655456</v>
+        <v>0.8411109393084598</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.699531957433643</v>
+        <v>4.572517580205707</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0727225382589522</v>
+        <v>0.07327494187710665</v>
       </c>
       <c r="C39">
-        <v>153.3194748610591</v>
+        <v>148.2605116892926</v>
       </c>
       <c r="D39">
-        <v>219.6534748610591</v>
+        <v>216.8765116892926</v>
       </c>
       <c r="E39">
-        <v>-36.166</v>
+        <v>-33.884</v>
       </c>
       <c r="F39">
-        <v>84.434</v>
+        <v>86.71599999999999</v>
       </c>
       <c r="G39">
         <v>18.1</v>
@@ -4485,45 +4485,45 @@
         <v>21.35</v>
       </c>
       <c r="M39">
-        <v>4.6692002</v>
+        <v>5.0121848</v>
       </c>
       <c r="N39">
-        <v>16.6807998</v>
+        <v>16.3378152</v>
       </c>
       <c r="O39">
-        <v>4.503815946000001</v>
+        <v>4.411210104</v>
       </c>
       <c r="P39">
-        <v>12.176983854</v>
+        <v>11.926605096</v>
       </c>
       <c r="Q39">
-        <v>23.576983854</v>
+        <v>23.326605096</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09172382263325746</v>
+        <v>0.09232455141468815</v>
       </c>
       <c r="T39">
-        <v>0.8411109393084598</v>
+        <v>0.8521134979075972</v>
       </c>
       <c r="U39">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V39">
         <v>0.27</v>
       </c>
       <c r="W39">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.572517580205707</v>
+        <v>4.259619477717582</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07327494187710665</v>
+        <v>0.07315209549526111</v>
       </c>
       <c r="C40">
-        <v>148.2605116892926</v>
+        <v>146.5899788738507</v>
       </c>
       <c r="D40">
-        <v>216.8765116892926</v>
+        <v>217.4879788738507</v>
       </c>
       <c r="E40">
-        <v>-33.884</v>
+        <v>-31.60199999999999</v>
       </c>
       <c r="F40">
-        <v>86.71599999999999</v>
+        <v>88.998</v>
       </c>
       <c r="G40">
         <v>18.1</v>
@@ -4567,28 +4567,28 @@
         <v>21.35</v>
       </c>
       <c r="M40">
-        <v>5.0121848</v>
+        <v>5.144084400000001</v>
       </c>
       <c r="N40">
-        <v>16.3378152</v>
+        <v>16.2059156</v>
       </c>
       <c r="O40">
-        <v>4.411210104</v>
+        <v>4.375597212000001</v>
       </c>
       <c r="P40">
-        <v>11.926605096</v>
+        <v>11.830318388</v>
       </c>
       <c r="Q40">
-        <v>23.326605096</v>
+        <v>23.230318388</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09232455141468815</v>
+        <v>0.09294497622173953</v>
       </c>
       <c r="T40">
-        <v>0.8521134979075972</v>
+        <v>0.8634767961329357</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.259619477717582</v>
+        <v>4.150398465468412</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07315209549526111</v>
+        <v>0.07302924911341557</v>
       </c>
       <c r="C41">
-        <v>146.5899788738507</v>
+        <v>144.9229037796383</v>
       </c>
       <c r="D41">
-        <v>217.4879788738507</v>
+        <v>218.1029037796383</v>
       </c>
       <c r="E41">
-        <v>-31.60199999999999</v>
+        <v>-29.31999999999999</v>
       </c>
       <c r="F41">
-        <v>88.998</v>
+        <v>91.28</v>
       </c>
       <c r="G41">
         <v>18.1</v>
@@ -4649,28 +4649,28 @@
         <v>21.35</v>
       </c>
       <c r="M41">
-        <v>5.144084400000001</v>
+        <v>5.275984</v>
       </c>
       <c r="N41">
-        <v>16.2059156</v>
+        <v>16.074016</v>
       </c>
       <c r="O41">
-        <v>4.375597212000001</v>
+        <v>4.33998432</v>
       </c>
       <c r="P41">
-        <v>11.830318388</v>
+        <v>11.73403168</v>
       </c>
       <c r="Q41">
-        <v>23.230318388</v>
+        <v>23.13403168</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09294497622173953</v>
+        <v>0.09358608185569263</v>
       </c>
       <c r="T41">
-        <v>0.8634767961329357</v>
+        <v>0.8752188709657855</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.150398465468412</v>
+        <v>4.046638503831702</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07302924911341557</v>
+        <v>0.07395395273157003</v>
       </c>
       <c r="C42">
-        <v>144.9229037796383</v>
+        <v>138.0958138629748</v>
       </c>
       <c r="D42">
-        <v>218.1029037796383</v>
+        <v>213.5578138629748</v>
       </c>
       <c r="E42">
-        <v>-29.31999999999999</v>
+        <v>-27.038</v>
       </c>
       <c r="F42">
-        <v>91.28</v>
+        <v>93.562</v>
       </c>
       <c r="G42">
         <v>18.1</v>
@@ -4731,45 +4731,45 @@
         <v>21.35</v>
       </c>
       <c r="M42">
-        <v>5.275984</v>
+        <v>5.7353506</v>
       </c>
       <c r="N42">
-        <v>16.074016</v>
+        <v>15.6146494</v>
       </c>
       <c r="O42">
-        <v>4.33998432</v>
+        <v>4.215955338000001</v>
       </c>
       <c r="P42">
-        <v>11.73403168</v>
+        <v>11.398694062</v>
       </c>
       <c r="Q42">
-        <v>23.13403168</v>
+        <v>22.798694062</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09358608185569263</v>
+        <v>0.09424891988401701</v>
       </c>
       <c r="T42">
-        <v>0.8752188709657855</v>
+        <v>0.8873589822336472</v>
       </c>
       <c r="U42">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V42">
         <v>0.27</v>
       </c>
       <c r="W42">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.046638503831702</v>
+        <v>3.722527442350255</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07395395273157003</v>
+        <v>0.07385665634972451</v>
       </c>
       <c r="C43">
-        <v>138.0958138629748</v>
+        <v>136.2831067220037</v>
       </c>
       <c r="D43">
-        <v>213.5578138629748</v>
+        <v>214.0271067220037</v>
       </c>
       <c r="E43">
-        <v>-27.038</v>
+        <v>-24.75599999999999</v>
       </c>
       <c r="F43">
-        <v>93.562</v>
+        <v>95.84400000000001</v>
       </c>
       <c r="G43">
         <v>18.1</v>
@@ -4813,28 +4813,28 @@
         <v>21.35</v>
       </c>
       <c r="M43">
-        <v>5.7353506</v>
+        <v>5.875237200000001</v>
       </c>
       <c r="N43">
-        <v>15.6146494</v>
+        <v>15.4747628</v>
       </c>
       <c r="O43">
-        <v>4.215955338000001</v>
+        <v>4.178185956</v>
       </c>
       <c r="P43">
-        <v>11.398694062</v>
+        <v>11.296576844</v>
       </c>
       <c r="Q43">
-        <v>22.798694062</v>
+        <v>22.696576844</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09424891988401701</v>
+        <v>0.09493461439607673</v>
       </c>
       <c r="T43">
-        <v>0.8873589822336472</v>
+        <v>0.8999177180279869</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.722527442350255</v>
+        <v>3.63389583658001</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07385665634972449</v>
+        <v>0.07375935996787897</v>
       </c>
       <c r="C44">
-        <v>136.2831067220037</v>
+        <v>134.4724666636375</v>
       </c>
       <c r="D44">
-        <v>214.0271067220037</v>
+        <v>214.4984666636375</v>
       </c>
       <c r="E44">
-        <v>-24.756</v>
+        <v>-22.474</v>
       </c>
       <c r="F44">
-        <v>95.84399999999999</v>
+        <v>98.12599999999999</v>
       </c>
       <c r="G44">
         <v>18.1</v>
@@ -4895,28 +4895,28 @@
         <v>21.35</v>
       </c>
       <c r="M44">
-        <v>5.8752372</v>
+        <v>6.0151238</v>
       </c>
       <c r="N44">
-        <v>15.4747628</v>
+        <v>15.3348762</v>
       </c>
       <c r="O44">
-        <v>4.178185956</v>
+        <v>4.140416574000001</v>
       </c>
       <c r="P44">
-        <v>11.296576844</v>
+        <v>11.194459626</v>
       </c>
       <c r="Q44">
-        <v>22.696576844</v>
+        <v>22.594459626</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.0949346143960767</v>
+        <v>0.09564436836469992</v>
       </c>
       <c r="T44">
-        <v>0.8999177180279867</v>
+        <v>0.9129171112186191</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.633895836580011</v>
+        <v>3.54938663107815</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07375935996787897</v>
+        <v>0.07456142358603342</v>
       </c>
       <c r="C45">
-        <v>134.4724666636375</v>
+        <v>128.3656879367129</v>
       </c>
       <c r="D45">
-        <v>214.4984666636375</v>
+        <v>210.6736879367129</v>
       </c>
       <c r="E45">
-        <v>-22.474</v>
+        <v>-20.19199999999999</v>
       </c>
       <c r="F45">
-        <v>98.12599999999999</v>
+        <v>100.408</v>
       </c>
       <c r="G45">
         <v>18.1</v>
@@ -4977,45 +4977,45 @@
         <v>21.35</v>
       </c>
       <c r="M45">
-        <v>6.0151238</v>
+        <v>6.4361528</v>
       </c>
       <c r="N45">
-        <v>15.3348762</v>
+        <v>14.9138472</v>
       </c>
       <c r="O45">
-        <v>4.140416574000001</v>
+        <v>4.026738744</v>
       </c>
       <c r="P45">
-        <v>11.194459626</v>
+        <v>10.887108456</v>
       </c>
       <c r="Q45">
-        <v>22.594459626</v>
+        <v>22.287108456</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09564436836469992</v>
+        <v>0.09637947068934538</v>
       </c>
       <c r="T45">
-        <v>0.9129171112186191</v>
+        <v>0.9263807684517739</v>
       </c>
       <c r="U45">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.27</v>
       </c>
       <c r="W45">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.54938663107815</v>
+        <v>3.317199057175896</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07456142358603342</v>
+        <v>0.07448456720418788</v>
       </c>
       <c r="C46">
-        <v>128.3656879367129</v>
+        <v>126.4442717536015</v>
       </c>
       <c r="D46">
-        <v>210.6736879367129</v>
+        <v>211.0342717536015</v>
       </c>
       <c r="E46">
-        <v>-20.19199999999999</v>
+        <v>-17.91</v>
       </c>
       <c r="F46">
-        <v>100.408</v>
+        <v>102.69</v>
       </c>
       <c r="G46">
         <v>18.1</v>
@@ -5059,28 +5059,28 @@
         <v>21.35</v>
       </c>
       <c r="M46">
-        <v>6.4361528</v>
+        <v>6.582429</v>
       </c>
       <c r="N46">
-        <v>14.9138472</v>
+        <v>14.767571</v>
       </c>
       <c r="O46">
-        <v>4.026738744</v>
+        <v>3.98724417</v>
       </c>
       <c r="P46">
-        <v>10.887108456</v>
+        <v>10.78032683</v>
       </c>
       <c r="Q46">
-        <v>22.287108456</v>
+        <v>22.18032683</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09637947068934538</v>
+        <v>0.09714130400761431</v>
       </c>
       <c r="T46">
-        <v>0.9263807684517739</v>
+        <v>0.9403340132206798</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.317199057175896</v>
+        <v>3.243483522571986</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07448456720418788</v>
+        <v>0.07440771082234235</v>
       </c>
       <c r="C47">
-        <v>126.4442717536015</v>
+        <v>124.5240920192557</v>
       </c>
       <c r="D47">
-        <v>211.0342717536015</v>
+        <v>211.3960920192557</v>
       </c>
       <c r="E47">
-        <v>-17.91</v>
+        <v>-15.628</v>
       </c>
       <c r="F47">
-        <v>102.69</v>
+        <v>104.972</v>
       </c>
       <c r="G47">
         <v>18.1</v>
@@ -5141,28 +5141,28 @@
         <v>21.35</v>
       </c>
       <c r="M47">
-        <v>6.582429</v>
+        <v>6.7287052</v>
       </c>
       <c r="N47">
-        <v>14.767571</v>
+        <v>14.6212948</v>
       </c>
       <c r="O47">
-        <v>3.98724417</v>
+        <v>3.947749596</v>
       </c>
       <c r="P47">
-        <v>10.78032683</v>
+        <v>10.673545204</v>
       </c>
       <c r="Q47">
-        <v>22.18032683</v>
+        <v>22.073545204</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09714130400761431</v>
+        <v>0.09793135337470803</v>
       </c>
       <c r="T47">
-        <v>0.9403340132206798</v>
+        <v>0.9548040448328786</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.243483522571986</v>
+        <v>3.172973011211726</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07440771082234235</v>
+        <v>0.07433085444049679</v>
       </c>
       <c r="C48">
-        <v>124.5240920192557</v>
+        <v>122.6051551043077</v>
       </c>
       <c r="D48">
-        <v>211.3960920192557</v>
+        <v>211.7591551043078</v>
       </c>
       <c r="E48">
-        <v>-15.628</v>
+        <v>-13.34599999999999</v>
       </c>
       <c r="F48">
-        <v>104.972</v>
+        <v>107.254</v>
       </c>
       <c r="G48">
         <v>18.1</v>
@@ -5223,28 +5223,28 @@
         <v>21.35</v>
       </c>
       <c r="M48">
-        <v>6.7287052</v>
+        <v>6.874981400000001</v>
       </c>
       <c r="N48">
-        <v>14.6212948</v>
+        <v>14.4750186</v>
       </c>
       <c r="O48">
-        <v>3.947749596</v>
+        <v>3.908255022000001</v>
       </c>
       <c r="P48">
-        <v>10.673545204</v>
+        <v>10.566763578</v>
       </c>
       <c r="Q48">
-        <v>22.073545204</v>
+        <v>21.966763578</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09793135337470803</v>
+        <v>0.09875121592546565</v>
       </c>
       <c r="T48">
-        <v>0.9548040448328786</v>
+        <v>0.9698201153738395</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.172973011211726</v>
+        <v>3.105462947143391</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07433085444049679</v>
+        <v>0.07425399805865127</v>
       </c>
       <c r="C49">
-        <v>122.6051551043077</v>
+        <v>120.6874674232298</v>
       </c>
       <c r="D49">
-        <v>211.7591551043078</v>
+        <v>212.1234674232298</v>
       </c>
       <c r="E49">
-        <v>-13.34599999999999</v>
+        <v>-11.06399999999999</v>
       </c>
       <c r="F49">
-        <v>107.254</v>
+        <v>109.536</v>
       </c>
       <c r="G49">
         <v>18.1</v>
@@ -5305,28 +5305,28 @@
         <v>21.35</v>
       </c>
       <c r="M49">
-        <v>6.874981400000001</v>
+        <v>7.0212576</v>
       </c>
       <c r="N49">
-        <v>14.4750186</v>
+        <v>14.3287424</v>
       </c>
       <c r="O49">
-        <v>3.908255022000001</v>
+        <v>3.868760448000001</v>
       </c>
       <c r="P49">
-        <v>10.566763578</v>
+        <v>10.459981952</v>
       </c>
       <c r="Q49">
-        <v>21.966763578</v>
+        <v>21.859981952</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09875121592546565</v>
+        <v>0.09960261165125241</v>
       </c>
       <c r="T49">
-        <v>0.9698201153738395</v>
+        <v>0.9854137270894529</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.105462947143391</v>
+        <v>3.040765802411238</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07425399805865125</v>
+        <v>0.07696720167680571</v>
       </c>
       <c r="C50">
-        <v>120.6874674232298</v>
+        <v>106.259944617848</v>
       </c>
       <c r="D50">
-        <v>212.1234674232298</v>
+        <v>199.977944617848</v>
       </c>
       <c r="E50">
-        <v>-11.06400000000001</v>
+        <v>-8.781999999999996</v>
       </c>
       <c r="F50">
-        <v>109.536</v>
+        <v>111.818</v>
       </c>
       <c r="G50">
         <v>18.1</v>
@@ -5387,45 +5387,45 @@
         <v>21.35</v>
       </c>
       <c r="M50">
-        <v>7.021257599999999</v>
+        <v>8.039714200000001</v>
       </c>
       <c r="N50">
-        <v>14.3287424</v>
+        <v>13.3102858</v>
       </c>
       <c r="O50">
-        <v>3.868760448000001</v>
+        <v>3.593777166000001</v>
       </c>
       <c r="P50">
-        <v>10.459981952</v>
+        <v>9.716508634</v>
       </c>
       <c r="Q50">
-        <v>21.859981952</v>
+        <v>21.116508634</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09960261165125241</v>
+        <v>0.1004873954447171</v>
       </c>
       <c r="T50">
-        <v>0.9854137270894529</v>
+        <v>1.001618852989992</v>
       </c>
       <c r="U50">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V50">
         <v>0.27</v>
       </c>
       <c r="W50">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.040765802411238</v>
+        <v>2.655567034957536</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07696720167680571</v>
+        <v>0.07694728529496017</v>
       </c>
       <c r="C51">
-        <v>106.259944617848</v>
+        <v>104.0620299461021</v>
       </c>
       <c r="D51">
-        <v>199.977944617848</v>
+        <v>200.0620299461021</v>
       </c>
       <c r="E51">
-        <v>-8.781999999999996</v>
+        <v>-6.5</v>
       </c>
       <c r="F51">
-        <v>111.818</v>
+        <v>114.1</v>
       </c>
       <c r="G51">
         <v>18.1</v>
@@ -5469,28 +5469,28 @@
         <v>21.35</v>
       </c>
       <c r="M51">
-        <v>8.039714200000001</v>
+        <v>8.20379</v>
       </c>
       <c r="N51">
-        <v>13.3102858</v>
+        <v>13.14621</v>
       </c>
       <c r="O51">
-        <v>3.593777166000001</v>
+        <v>3.5494767</v>
       </c>
       <c r="P51">
-        <v>9.716508634</v>
+        <v>9.5967333</v>
       </c>
       <c r="Q51">
-        <v>21.116508634</v>
+        <v>20.9967333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1004873954447171</v>
+        <v>0.1014075705899203</v>
       </c>
       <c r="T51">
-        <v>1.001618852989992</v>
+        <v>1.018472183926553</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.655567034957536</v>
+        <v>2.602455694258386</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07694728529496017</v>
+        <v>0.07692736891311464</v>
       </c>
       <c r="C52">
-        <v>104.0620299461021</v>
+        <v>101.8641860153229</v>
       </c>
       <c r="D52">
-        <v>200.0620299461021</v>
+        <v>200.1461860153229</v>
       </c>
       <c r="E52">
-        <v>-6.5</v>
+        <v>-4.218000000000004</v>
       </c>
       <c r="F52">
-        <v>114.1</v>
+        <v>116.382</v>
       </c>
       <c r="G52">
         <v>18.1</v>
@@ -5551,28 +5551,28 @@
         <v>21.35</v>
       </c>
       <c r="M52">
-        <v>8.20379</v>
+        <v>8.367865800000001</v>
       </c>
       <c r="N52">
-        <v>13.14621</v>
+        <v>12.9821342</v>
       </c>
       <c r="O52">
-        <v>3.5494767</v>
+        <v>3.505176234</v>
       </c>
       <c r="P52">
-        <v>9.5967333</v>
+        <v>9.476957966000001</v>
       </c>
       <c r="Q52">
-        <v>20.9967333</v>
+        <v>20.876957966</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1014075705899203</v>
+        <v>0.1023653039043156</v>
       </c>
       <c r="T52">
-        <v>1.018472183926553</v>
+        <v>1.036013405921749</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.602455694258386</v>
+        <v>2.551427151233711</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07692736891311464</v>
+        <v>0.0769074525312691</v>
       </c>
       <c r="C53">
-        <v>101.8641860153229</v>
+        <v>99.66641291481965</v>
       </c>
       <c r="D53">
-        <v>200.1461860153229</v>
+        <v>200.2304129148197</v>
       </c>
       <c r="E53">
-        <v>-4.218000000000004</v>
+        <v>-1.935999999999993</v>
       </c>
       <c r="F53">
-        <v>116.382</v>
+        <v>118.664</v>
       </c>
       <c r="G53">
         <v>18.1</v>
@@ -5633,28 +5633,28 @@
         <v>21.35</v>
       </c>
       <c r="M53">
-        <v>8.367865800000001</v>
+        <v>8.531941600000001</v>
       </c>
       <c r="N53">
-        <v>12.9821342</v>
+        <v>12.8180584</v>
       </c>
       <c r="O53">
-        <v>3.505176234</v>
+        <v>3.460875768</v>
       </c>
       <c r="P53">
-        <v>9.476957966000001</v>
+        <v>9.357182632000001</v>
       </c>
       <c r="Q53">
-        <v>20.876957966</v>
+        <v>20.757182632</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1023653039043156</v>
+        <v>0.1033629427734773</v>
       </c>
       <c r="T53">
-        <v>1.036013405921749</v>
+        <v>1.054285512166745</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.551427151233711</v>
+        <v>2.502361244479216</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0769074525312691</v>
+        <v>0.07839644614942355</v>
       </c>
       <c r="C54">
-        <v>99.66641291481965</v>
+        <v>91.27692366548683</v>
       </c>
       <c r="D54">
-        <v>200.2304129148197</v>
+        <v>194.1229236654868</v>
       </c>
       <c r="E54">
-        <v>-1.935999999999993</v>
+        <v>0.3460000000000036</v>
       </c>
       <c r="F54">
-        <v>118.664</v>
+        <v>120.946</v>
       </c>
       <c r="G54">
         <v>18.1</v>
@@ -5715,45 +5715,45 @@
         <v>21.35</v>
       </c>
       <c r="M54">
-        <v>8.531941600000001</v>
+        <v>9.167706800000001</v>
       </c>
       <c r="N54">
-        <v>12.8180584</v>
+        <v>12.1822932</v>
       </c>
       <c r="O54">
-        <v>3.460875768</v>
+        <v>3.289219164</v>
       </c>
       <c r="P54">
-        <v>9.357182632000001</v>
+        <v>8.893074036</v>
       </c>
       <c r="Q54">
-        <v>20.757182632</v>
+        <v>20.293074036</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1033629427734773</v>
+        <v>0.1044030343604756</v>
       </c>
       <c r="T54">
-        <v>1.054285512166745</v>
+        <v>1.073335154847698</v>
       </c>
       <c r="U54">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V54">
         <v>0.27</v>
       </c>
       <c r="W54">
-        <v>0.05248700000000001</v>
+        <v>0.055334</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.502361244479216</v>
+        <v>2.328826659246999</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07839644614942355</v>
+        <v>0.078404999767578</v>
       </c>
       <c r="C55">
-        <v>91.27692366548683</v>
+        <v>88.96091493481663</v>
       </c>
       <c r="D55">
-        <v>194.1229236654868</v>
+        <v>194.0889149348166</v>
       </c>
       <c r="E55">
-        <v>0.3460000000000036</v>
+        <v>2.628000000000014</v>
       </c>
       <c r="F55">
-        <v>120.946</v>
+        <v>123.228</v>
       </c>
       <c r="G55">
         <v>18.1</v>
@@ -5797,28 +5797,28 @@
         <v>21.35</v>
       </c>
       <c r="M55">
-        <v>9.167706800000001</v>
+        <v>9.340682400000002</v>
       </c>
       <c r="N55">
-        <v>12.1822932</v>
+        <v>12.0093176</v>
       </c>
       <c r="O55">
-        <v>3.289219164</v>
+        <v>3.242515752</v>
       </c>
       <c r="P55">
-        <v>8.893074036</v>
+        <v>8.766801848</v>
       </c>
       <c r="Q55">
-        <v>20.293074036</v>
+        <v>20.166801848</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1044030343604756</v>
+        <v>0.1054883473208218</v>
       </c>
       <c r="T55">
-        <v>1.073335154847698</v>
+        <v>1.093213042862606</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.328826659246999</v>
+        <v>2.285700239631314</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.078404999767578</v>
+        <v>0.07841355338573247</v>
       </c>
       <c r="C56">
-        <v>88.96091493481663</v>
+        <v>86.64491811815584</v>
       </c>
       <c r="D56">
-        <v>194.0889149348166</v>
+        <v>194.0549181181559</v>
       </c>
       <c r="E56">
-        <v>2.628000000000014</v>
+        <v>4.910000000000011</v>
       </c>
       <c r="F56">
-        <v>123.228</v>
+        <v>125.51</v>
       </c>
       <c r="G56">
         <v>18.1</v>
@@ -5879,28 +5879,28 @@
         <v>21.35</v>
       </c>
       <c r="M56">
-        <v>9.340682400000002</v>
+        <v>9.513658000000001</v>
       </c>
       <c r="N56">
-        <v>12.0093176</v>
+        <v>11.836342</v>
       </c>
       <c r="O56">
-        <v>3.242515752</v>
+        <v>3.19581234</v>
       </c>
       <c r="P56">
-        <v>8.766801848</v>
+        <v>8.64052966</v>
       </c>
       <c r="Q56">
-        <v>20.166801848</v>
+        <v>20.04052966</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1054883473208218</v>
+        <v>0.1066218964127388</v>
       </c>
       <c r="T56">
-        <v>1.093213042862606</v>
+        <v>1.113974392567065</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.285700239631314</v>
+        <v>2.2441420534562</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07841355338573247</v>
+        <v>0.07842210700388694</v>
       </c>
       <c r="C57">
-        <v>86.64491811815584</v>
+        <v>84.32893320924495</v>
       </c>
       <c r="D57">
-        <v>194.0549181181559</v>
+        <v>194.020933209245</v>
       </c>
       <c r="E57">
-        <v>4.910000000000011</v>
+        <v>7.192000000000007</v>
       </c>
       <c r="F57">
-        <v>125.51</v>
+        <v>127.792</v>
       </c>
       <c r="G57">
         <v>18.1</v>
@@ -5961,28 +5961,28 @@
         <v>21.35</v>
       </c>
       <c r="M57">
-        <v>9.513658000000001</v>
+        <v>9.6866336</v>
       </c>
       <c r="N57">
-        <v>11.836342</v>
+        <v>11.6633664</v>
       </c>
       <c r="O57">
-        <v>3.19581234</v>
+        <v>3.149108928</v>
       </c>
       <c r="P57">
-        <v>8.64052966</v>
+        <v>8.514257472000001</v>
       </c>
       <c r="Q57">
-        <v>20.04052966</v>
+        <v>19.914257472</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1066218964127388</v>
+        <v>0.1078069704633794</v>
       </c>
       <c r="T57">
-        <v>1.113974392567065</v>
+        <v>1.135679439985363</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.2441420534562</v>
+        <v>2.20406808821591</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07842210700388694</v>
+        <v>0.0784306606220414</v>
       </c>
       <c r="C58">
-        <v>84.32893320924495</v>
+        <v>82.0129602018288</v>
       </c>
       <c r="D58">
-        <v>194.020933209245</v>
+        <v>193.9869602018288</v>
       </c>
       <c r="E58">
-        <v>7.192000000000007</v>
+        <v>9.474000000000018</v>
       </c>
       <c r="F58">
-        <v>127.792</v>
+        <v>130.074</v>
       </c>
       <c r="G58">
         <v>18.1</v>
@@ -6043,28 +6043,28 @@
         <v>21.35</v>
       </c>
       <c r="M58">
-        <v>9.6866336</v>
+        <v>9.859609200000001</v>
       </c>
       <c r="N58">
-        <v>11.6633664</v>
+        <v>11.4903908</v>
       </c>
       <c r="O58">
-        <v>3.149108928</v>
+        <v>3.102405516</v>
       </c>
       <c r="P58">
-        <v>8.514257472000001</v>
+        <v>8.387985283999999</v>
       </c>
       <c r="Q58">
-        <v>19.914257472</v>
+        <v>19.787985284</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1078069704633794</v>
+        <v>0.1090471642373056</v>
       </c>
       <c r="T58">
-        <v>1.135679439985363</v>
+        <v>1.158394024492885</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.20406808821591</v>
+        <v>2.165400227019139</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0784306606220414</v>
+        <v>0.07843921424019586</v>
       </c>
       <c r="C59">
-        <v>82.0129602018288</v>
+        <v>79.6969990896568</v>
       </c>
       <c r="D59">
-        <v>193.9869602018288</v>
+        <v>193.9529990896568</v>
       </c>
       <c r="E59">
-        <v>9.474000000000018</v>
+        <v>11.75600000000003</v>
       </c>
       <c r="F59">
-        <v>130.074</v>
+        <v>132.356</v>
       </c>
       <c r="G59">
         <v>18.1</v>
@@ -6125,28 +6125,28 @@
         <v>21.35</v>
       </c>
       <c r="M59">
-        <v>9.859609200000001</v>
+        <v>10.0325848</v>
       </c>
       <c r="N59">
-        <v>11.4903908</v>
+        <v>11.3174152</v>
       </c>
       <c r="O59">
-        <v>3.102405516</v>
+        <v>3.055702104</v>
       </c>
       <c r="P59">
-        <v>8.387985283999999</v>
+        <v>8.261713095999999</v>
       </c>
       <c r="Q59">
-        <v>19.787985284</v>
+        <v>19.661713096</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1090471642373056</v>
+        <v>0.1103464148576092</v>
       </c>
       <c r="T59">
-        <v>1.158394024492885</v>
+        <v>1.182190255881716</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.165400227019139</v>
+        <v>2.128065740346396</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07843921424019584</v>
+        <v>0.07844776785835031</v>
       </c>
       <c r="C60">
-        <v>79.69699908965688</v>
+        <v>77.38104986648247</v>
       </c>
       <c r="D60">
-        <v>193.9529990896569</v>
+        <v>193.9190498664825</v>
       </c>
       <c r="E60">
-        <v>11.756</v>
+        <v>14.03799999999998</v>
       </c>
       <c r="F60">
-        <v>132.356</v>
+        <v>134.638</v>
       </c>
       <c r="G60">
         <v>18.1</v>
@@ -6207,28 +6207,28 @@
         <v>21.35</v>
       </c>
       <c r="M60">
-        <v>10.0325848</v>
+        <v>10.2055604</v>
       </c>
       <c r="N60">
-        <v>11.3174152</v>
+        <v>11.1444396</v>
       </c>
       <c r="O60">
-        <v>3.055702104</v>
+        <v>3.008998692000001</v>
       </c>
       <c r="P60">
-        <v>8.261713096000001</v>
+        <v>8.135440908000001</v>
       </c>
       <c r="Q60">
-        <v>19.661713096</v>
+        <v>19.535440908</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1103464148576092</v>
+        <v>0.111709043556952</v>
       </c>
       <c r="T60">
-        <v>1.182190255881716</v>
+        <v>1.207147279045613</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.128065740346396</v>
+        <v>2.091996829493068</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07844776785835031</v>
+        <v>0.07845632147650478</v>
       </c>
       <c r="C61">
-        <v>77.38104986648247</v>
+        <v>75.0651125260637</v>
       </c>
       <c r="D61">
-        <v>193.9190498664825</v>
+        <v>193.8851125260637</v>
       </c>
       <c r="E61">
-        <v>14.03799999999998</v>
+        <v>16.31999999999999</v>
       </c>
       <c r="F61">
-        <v>134.638</v>
+        <v>136.92</v>
       </c>
       <c r="G61">
         <v>18.1</v>
@@ -6289,28 +6289,28 @@
         <v>21.35</v>
       </c>
       <c r="M61">
-        <v>10.2055604</v>
+        <v>10.378536</v>
       </c>
       <c r="N61">
-        <v>11.1444396</v>
+        <v>10.971464</v>
       </c>
       <c r="O61">
-        <v>3.008998692000001</v>
+        <v>2.962295280000001</v>
       </c>
       <c r="P61">
-        <v>8.135440908000001</v>
+        <v>8.00916872</v>
       </c>
       <c r="Q61">
-        <v>19.535440908</v>
+        <v>19.40916872</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.111709043556952</v>
+        <v>0.1131398036912619</v>
       </c>
       <c r="T61">
-        <v>1.207147279045613</v>
+        <v>1.233352153367704</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.091996829493068</v>
+        <v>2.057130215668183</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07845632147650478</v>
+        <v>0.07846487509465923</v>
       </c>
       <c r="C62">
-        <v>75.0651125260637</v>
+        <v>72.74918706216303</v>
       </c>
       <c r="D62">
-        <v>193.8851125260637</v>
+        <v>193.851187062163</v>
       </c>
       <c r="E62">
-        <v>16.31999999999999</v>
+        <v>18.602</v>
       </c>
       <c r="F62">
-        <v>136.92</v>
+        <v>139.202</v>
       </c>
       <c r="G62">
         <v>18.1</v>
@@ -6371,28 +6371,28 @@
         <v>21.35</v>
       </c>
       <c r="M62">
-        <v>10.378536</v>
+        <v>10.5515116</v>
       </c>
       <c r="N62">
-        <v>10.971464</v>
+        <v>10.7984884</v>
       </c>
       <c r="O62">
-        <v>2.962295280000001</v>
+        <v>2.915591868</v>
       </c>
       <c r="P62">
-        <v>8.00916872</v>
+        <v>7.882896532</v>
       </c>
       <c r="Q62">
-        <v>19.40916872</v>
+        <v>19.282896532</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1131398036912619</v>
+        <v>0.1146439361401519</v>
       </c>
       <c r="T62">
-        <v>1.233352153367704</v>
+        <v>1.260900867398621</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.057130215668183</v>
+        <v>2.023406769509688</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07846487509465923</v>
+        <v>0.08490034871281368</v>
       </c>
       <c r="C63">
-        <v>72.74918706216303</v>
+        <v>47.91600262108904</v>
       </c>
       <c r="D63">
-        <v>193.851187062163</v>
+        <v>171.300002621089</v>
       </c>
       <c r="E63">
-        <v>18.602</v>
+        <v>20.88399999999999</v>
       </c>
       <c r="F63">
-        <v>139.202</v>
+        <v>141.484</v>
       </c>
       <c r="G63">
         <v>18.1</v>
@@ -6453,45 +6453,45 @@
         <v>21.35</v>
       </c>
       <c r="M63">
-        <v>10.5515116</v>
+        <v>12.73356</v>
       </c>
       <c r="N63">
-        <v>10.7984884</v>
+        <v>8.616440000000004</v>
       </c>
       <c r="O63">
-        <v>2.915591868</v>
+        <v>2.326438800000001</v>
       </c>
       <c r="P63">
-        <v>7.882896532</v>
+        <v>6.290001200000003</v>
       </c>
       <c r="Q63">
-        <v>19.282896532</v>
+        <v>17.6900012</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1146439361401519</v>
+        <v>0.1162272334547729</v>
       </c>
       <c r="T63">
-        <v>1.260900867398621</v>
+        <v>1.289899513746955</v>
       </c>
       <c r="U63">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V63">
         <v>0.27</v>
       </c>
       <c r="W63">
-        <v>0.055334</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.023406769509688</v>
+        <v>1.676671724168261</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08490034871281368</v>
+        <v>0.08501256233096813</v>
       </c>
       <c r="C64">
-        <v>47.91600262108904</v>
+        <v>45.28723123244853</v>
       </c>
       <c r="D64">
-        <v>171.300002621089</v>
+        <v>170.9532312324485</v>
       </c>
       <c r="E64">
-        <v>20.88399999999999</v>
+        <v>23.166</v>
       </c>
       <c r="F64">
-        <v>141.484</v>
+        <v>143.766</v>
       </c>
       <c r="G64">
         <v>18.1</v>
@@ -6535,28 +6535,28 @@
         <v>21.35</v>
       </c>
       <c r="M64">
-        <v>12.73356</v>
+        <v>12.93894</v>
       </c>
       <c r="N64">
-        <v>8.616440000000004</v>
+        <v>8.411060000000003</v>
       </c>
       <c r="O64">
-        <v>2.326438800000001</v>
+        <v>2.270986200000001</v>
       </c>
       <c r="P64">
-        <v>6.290001200000003</v>
+        <v>6.140073800000001</v>
       </c>
       <c r="Q64">
-        <v>17.6900012</v>
+        <v>17.5400738</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1162272334547729</v>
+        <v>0.117896114408022</v>
       </c>
       <c r="T64">
-        <v>1.289899513746955</v>
+        <v>1.320465654492496</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.676671724168261</v>
+        <v>1.650057887276701</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08501256233096813</v>
+        <v>0.0851247759491226</v>
       </c>
       <c r="C65">
-        <v>45.28723123244853</v>
+        <v>42.65986098165834</v>
       </c>
       <c r="D65">
-        <v>170.9532312324485</v>
+        <v>170.6078609816583</v>
       </c>
       <c r="E65">
-        <v>23.166</v>
+        <v>25.44800000000001</v>
       </c>
       <c r="F65">
-        <v>143.766</v>
+        <v>146.048</v>
       </c>
       <c r="G65">
         <v>18.1</v>
@@ -6617,28 +6617,28 @@
         <v>21.35</v>
       </c>
       <c r="M65">
-        <v>12.93894</v>
+        <v>13.14432</v>
       </c>
       <c r="N65">
-        <v>8.411060000000003</v>
+        <v>8.205680000000001</v>
       </c>
       <c r="O65">
-        <v>2.270986200000001</v>
+        <v>2.215533600000001</v>
       </c>
       <c r="P65">
-        <v>6.140073800000001</v>
+        <v>5.9901464</v>
       </c>
       <c r="Q65">
-        <v>17.5400738</v>
+        <v>17.3901464</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.117896114408022</v>
+        <v>0.119657710969785</v>
       </c>
       <c r="T65">
-        <v>1.320465654492496</v>
+        <v>1.352729914168344</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.650057887276701</v>
+        <v>1.624275732788003</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0851247759491226</v>
+        <v>0.08523698956727707</v>
       </c>
       <c r="C66">
-        <v>42.65986098165834</v>
+        <v>40.03388339384495</v>
       </c>
       <c r="D66">
-        <v>170.6078609816583</v>
+        <v>170.2638833938449</v>
       </c>
       <c r="E66">
-        <v>25.44800000000001</v>
+        <v>27.72999999999999</v>
       </c>
       <c r="F66">
-        <v>146.048</v>
+        <v>148.33</v>
       </c>
       <c r="G66">
         <v>18.1</v>
@@ -6699,28 +6699,28 @@
         <v>21.35</v>
       </c>
       <c r="M66">
-        <v>13.14432</v>
+        <v>13.3497</v>
       </c>
       <c r="N66">
-        <v>8.205680000000001</v>
+        <v>8.000300000000003</v>
       </c>
       <c r="O66">
-        <v>2.215533600000001</v>
+        <v>2.160081000000001</v>
       </c>
       <c r="P66">
-        <v>5.9901464</v>
+        <v>5.840219000000002</v>
       </c>
       <c r="Q66">
-        <v>17.3901464</v>
+        <v>17.240219</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.119657710969785</v>
+        <v>0.1215199701922202</v>
       </c>
       <c r="T66">
-        <v>1.352729914168344</v>
+        <v>1.38683784582567</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.624275732788003</v>
+        <v>1.599286875360495</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08523698956727707</v>
+        <v>0.08534920318543152</v>
       </c>
       <c r="C67">
-        <v>40.03388339384495</v>
+        <v>37.40929006234506</v>
       </c>
       <c r="D67">
-        <v>170.2638833938449</v>
+        <v>169.9212900623451</v>
       </c>
       <c r="E67">
-        <v>27.72999999999999</v>
+        <v>30.012</v>
       </c>
       <c r="F67">
-        <v>148.33</v>
+        <v>150.612</v>
       </c>
       <c r="G67">
         <v>18.1</v>
@@ -6781,28 +6781,28 @@
         <v>21.35</v>
       </c>
       <c r="M67">
-        <v>13.3497</v>
+        <v>13.55508</v>
       </c>
       <c r="N67">
-        <v>8.000300000000003</v>
+        <v>7.794920000000003</v>
       </c>
       <c r="O67">
-        <v>2.160081000000001</v>
+        <v>2.104628400000001</v>
       </c>
       <c r="P67">
-        <v>5.840219000000002</v>
+        <v>5.690291600000002</v>
       </c>
       <c r="Q67">
-        <v>17.240219</v>
+        <v>17.0902916</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1215199701922202</v>
+        <v>0.1234917740747986</v>
       </c>
       <c r="T67">
-        <v>1.38683784582567</v>
+        <v>1.422952126404015</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.599286875360495</v>
+        <v>1.575055256036851</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08534920318543152</v>
+        <v>0.08546141680358597</v>
       </c>
       <c r="C68">
-        <v>37.40929006234506</v>
+        <v>34.78607264802062</v>
       </c>
       <c r="D68">
-        <v>169.9212900623451</v>
+        <v>169.5800726480206</v>
       </c>
       <c r="E68">
-        <v>30.012</v>
+        <v>32.29400000000001</v>
       </c>
       <c r="F68">
-        <v>150.612</v>
+        <v>152.894</v>
       </c>
       <c r="G68">
         <v>18.1</v>
@@ -6863,28 +6863,28 @@
         <v>21.35</v>
       </c>
       <c r="M68">
-        <v>13.55508</v>
+        <v>13.76046</v>
       </c>
       <c r="N68">
-        <v>7.794920000000003</v>
+        <v>7.589540000000001</v>
       </c>
       <c r="O68">
-        <v>2.104628400000001</v>
+        <v>2.0491758</v>
       </c>
       <c r="P68">
-        <v>5.690291600000002</v>
+        <v>5.540364200000001</v>
       </c>
       <c r="Q68">
-        <v>17.0902916</v>
+        <v>16.9403642</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1234917740747986</v>
+        <v>0.1255830812229878</v>
       </c>
       <c r="T68">
-        <v>1.422952126404015</v>
+        <v>1.461255151259835</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.575055256036851</v>
+        <v>1.551546968633316</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08546141680358597</v>
+        <v>0.08557363042174045</v>
       </c>
       <c r="C69">
-        <v>34.78607264802062</v>
+        <v>32.16422287858245</v>
       </c>
       <c r="D69">
-        <v>169.5800726480206</v>
+        <v>169.2402228785825</v>
       </c>
       <c r="E69">
-        <v>32.29400000000001</v>
+        <v>34.57600000000002</v>
       </c>
       <c r="F69">
-        <v>152.894</v>
+        <v>155.176</v>
       </c>
       <c r="G69">
         <v>18.1</v>
@@ -6945,28 +6945,28 @@
         <v>21.35</v>
       </c>
       <c r="M69">
-        <v>13.76046</v>
+        <v>13.96584</v>
       </c>
       <c r="N69">
-        <v>7.589540000000001</v>
+        <v>7.38416</v>
       </c>
       <c r="O69">
-        <v>2.0491758</v>
+        <v>1.9937232</v>
       </c>
       <c r="P69">
-        <v>5.540364200000001</v>
+        <v>5.3904368</v>
       </c>
       <c r="Q69">
-        <v>16.9403642</v>
+        <v>16.7904368</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1255830812229878</v>
+        <v>0.1278050950679389</v>
       </c>
       <c r="T69">
-        <v>1.461255151259835</v>
+        <v>1.501952115169144</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.551546968633316</v>
+        <v>1.528730101447532</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08557363042174045</v>
+        <v>0.0856858440398949</v>
       </c>
       <c r="C70">
-        <v>32.16422287858245</v>
+        <v>29.54373254792165</v>
       </c>
       <c r="D70">
-        <v>169.2402228785825</v>
+        <v>168.9017325479217</v>
       </c>
       <c r="E70">
-        <v>34.57600000000002</v>
+        <v>36.858</v>
       </c>
       <c r="F70">
-        <v>155.176</v>
+        <v>157.458</v>
       </c>
       <c r="G70">
         <v>18.1</v>
@@ -7027,28 +7027,28 @@
         <v>21.35</v>
       </c>
       <c r="M70">
-        <v>13.96584</v>
+        <v>14.17122</v>
       </c>
       <c r="N70">
-        <v>7.38416</v>
+        <v>7.178780000000001</v>
       </c>
       <c r="O70">
-        <v>1.9937232</v>
+        <v>1.938270600000001</v>
       </c>
       <c r="P70">
-        <v>5.3904368</v>
+        <v>5.240509400000001</v>
       </c>
       <c r="Q70">
-        <v>16.7904368</v>
+        <v>16.6405094</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1278050950679389</v>
+        <v>0.1301704646448223</v>
       </c>
       <c r="T70">
-        <v>1.501952115169144</v>
+        <v>1.545274689653247</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.528730101447532</v>
+        <v>1.506574592730901</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0856858440398949</v>
+        <v>0.1178513158717306</v>
       </c>
       <c r="C71">
-        <v>29.54373254792165</v>
+        <v>-34.28538857021604</v>
       </c>
       <c r="D71">
-        <v>168.9017325479217</v>
+        <v>107.354611429784</v>
       </c>
       <c r="E71">
-        <v>36.858</v>
+        <v>39.14000000000001</v>
       </c>
       <c r="F71">
-        <v>157.458</v>
+        <v>159.74</v>
       </c>
       <c r="G71">
         <v>18.1</v>
@@ -7109,45 +7109,45 @@
         <v>21.35</v>
       </c>
       <c r="M71">
-        <v>14.17122</v>
+        <v>23.449832</v>
       </c>
       <c r="N71">
-        <v>7.178780000000001</v>
+        <v>-2.099832000000003</v>
       </c>
       <c r="O71">
-        <v>1.938270600000001</v>
+        <v>-0.5669546400000008</v>
       </c>
       <c r="P71">
-        <v>5.240509400000001</v>
+        <v>-1.532877360000002</v>
       </c>
       <c r="Q71">
-        <v>16.6405094</v>
+        <v>9.867122639999996</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1301704646448223</v>
+        <v>0.1345068402268319</v>
       </c>
       <c r="T71">
-        <v>1.545274689653247</v>
+        <v>1.624696931309956</v>
       </c>
       <c r="U71">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.27</v>
+        <v>0.2458226566399281</v>
       </c>
       <c r="W71">
-        <v>0.06569999999999999</v>
+        <v>0.1107132340052586</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y71">
-        <v>1.506574592730901</v>
+        <v>0.9104542838515857</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1178513158717306</v>
+        <v>0.1188613158717306</v>
       </c>
       <c r="C72">
-        <v>-34.28538857021604</v>
+        <v>-37.78185292213843</v>
       </c>
       <c r="D72">
-        <v>107.354611429784</v>
+        <v>106.1401470778616</v>
       </c>
       <c r="E72">
-        <v>39.14000000000001</v>
+        <v>41.42200000000003</v>
       </c>
       <c r="F72">
-        <v>159.74</v>
+        <v>162.022</v>
       </c>
       <c r="G72">
         <v>18.1</v>
@@ -7191,37 +7191,37 @@
         <v>21.35</v>
       </c>
       <c r="M72">
-        <v>23.449832</v>
+        <v>23.78482960000001</v>
       </c>
       <c r="N72">
-        <v>-2.099832000000003</v>
+        <v>-2.434829600000004</v>
       </c>
       <c r="O72">
-        <v>-0.5669546400000008</v>
+        <v>-0.6574039920000011</v>
       </c>
       <c r="P72">
-        <v>-1.532877360000002</v>
+        <v>-1.777425608000003</v>
       </c>
       <c r="Q72">
-        <v>9.867122639999996</v>
+        <v>9.622574391999995</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1345068402268319</v>
+        <v>0.1375656967863779</v>
       </c>
       <c r="T72">
-        <v>1.624696931309956</v>
+        <v>1.680720963424092</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2458226566399281</v>
+        <v>0.2423603657013376</v>
       </c>
       <c r="W72">
-        <v>0.1107132340052586</v>
+        <v>0.1112214983150437</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.9104542838515857</v>
+        <v>0.8976309840790281</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1188613158717306</v>
+        <v>0.1198713158717306</v>
       </c>
       <c r="C73">
-        <v>-37.7818529221384</v>
+        <v>-41.25114703886305</v>
       </c>
       <c r="D73">
-        <v>106.1401470778616</v>
+        <v>104.9528529611369</v>
       </c>
       <c r="E73">
-        <v>41.422</v>
+        <v>43.70399999999998</v>
       </c>
       <c r="F73">
-        <v>162.022</v>
+        <v>164.304</v>
       </c>
       <c r="G73">
         <v>18.1</v>
@@ -7273,37 +7273,37 @@
         <v>21.35</v>
       </c>
       <c r="M73">
-        <v>23.7848296</v>
+        <v>24.1198272</v>
       </c>
       <c r="N73">
-        <v>-2.4348296</v>
+        <v>-2.769827199999998</v>
       </c>
       <c r="O73">
-        <v>-0.6574039920000002</v>
+        <v>-0.7478533439999996</v>
       </c>
       <c r="P73">
-        <v>-1.777425608</v>
+        <v>-2.021973855999998</v>
       </c>
       <c r="Q73">
-        <v>9.622574391999999</v>
+        <v>9.378026144</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1375656967863778</v>
+        <v>0.140843043100177</v>
       </c>
       <c r="T73">
-        <v>1.680720963424092</v>
+        <v>1.740746712117809</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2423603657013376</v>
+        <v>0.2389942495110413</v>
       </c>
       <c r="W73">
-        <v>0.1112214983150437</v>
+        <v>0.1117156441717791</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8976309840790282</v>
+        <v>0.8851638870779307</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1198713158717306</v>
+        <v>0.1208813158717305</v>
       </c>
       <c r="C74">
-        <v>-41.25114703886305</v>
+        <v>-44.6941726206461</v>
       </c>
       <c r="D74">
-        <v>104.9528529611369</v>
+        <v>103.7918273793539</v>
       </c>
       <c r="E74">
-        <v>43.70399999999998</v>
+        <v>45.98599999999999</v>
       </c>
       <c r="F74">
-        <v>164.304</v>
+        <v>166.586</v>
       </c>
       <c r="G74">
         <v>18.1</v>
@@ -7355,37 +7355,37 @@
         <v>21.35</v>
       </c>
       <c r="M74">
-        <v>24.1198272</v>
+        <v>24.4548248</v>
       </c>
       <c r="N74">
-        <v>-2.769827199999998</v>
+        <v>-3.104824799999999</v>
       </c>
       <c r="O74">
-        <v>-0.7478533439999996</v>
+        <v>-0.8383026959999998</v>
       </c>
       <c r="P74">
-        <v>-2.021973855999998</v>
+        <v>-2.266522103999999</v>
       </c>
       <c r="Q74">
-        <v>9.378026144</v>
+        <v>9.133477895999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.140843043100177</v>
+        <v>0.144363155807591</v>
       </c>
       <c r="T74">
-        <v>1.740746712117809</v>
+        <v>1.805218812566616</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2389942495110413</v>
+        <v>0.2357203556821229</v>
       </c>
       <c r="W74">
-        <v>0.1117156441717791</v>
+        <v>0.1121962517858644</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8851638870779307</v>
+        <v>0.873038354378233</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1208813158717305</v>
+        <v>0.1218913158717305</v>
       </c>
       <c r="C75">
-        <v>-44.6941726206461</v>
+        <v>-48.11179190459023</v>
       </c>
       <c r="D75">
-        <v>103.7918273793539</v>
+        <v>102.6562080954098</v>
       </c>
       <c r="E75">
-        <v>45.98599999999999</v>
+        <v>48.268</v>
       </c>
       <c r="F75">
-        <v>166.586</v>
+        <v>168.868</v>
       </c>
       <c r="G75">
         <v>18.1</v>
@@ -7437,37 +7437,37 @@
         <v>21.35</v>
       </c>
       <c r="M75">
-        <v>24.4548248</v>
+        <v>24.7898224</v>
       </c>
       <c r="N75">
-        <v>-3.104824799999999</v>
+        <v>-3.439822400000001</v>
       </c>
       <c r="O75">
-        <v>-0.8383026959999998</v>
+        <v>-0.9287520480000002</v>
       </c>
       <c r="P75">
-        <v>-2.266522103999999</v>
+        <v>-2.511070352</v>
       </c>
       <c r="Q75">
-        <v>9.133477895999999</v>
+        <v>8.888929647999998</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.144363155807591</v>
+        <v>0.1481540464155753</v>
       </c>
       <c r="T75">
-        <v>1.805218812566616</v>
+        <v>1.87465030535764</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2357203556821229</v>
+        <v>0.2325349454702023</v>
       </c>
       <c r="W75">
-        <v>0.1121962517858644</v>
+        <v>0.1126638700049743</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.873038354378233</v>
+        <v>0.8612405387785271</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1218913158717305</v>
+        <v>0.1229013158717306</v>
       </c>
       <c r="C76">
-        <v>-48.11179190459023</v>
+        <v>-51.50482980017355</v>
       </c>
       <c r="D76">
-        <v>102.6562080954098</v>
+        <v>101.5451701998264</v>
       </c>
       <c r="E76">
-        <v>48.268</v>
+        <v>50.54999999999998</v>
       </c>
       <c r="F76">
-        <v>168.868</v>
+        <v>171.15</v>
       </c>
       <c r="G76">
         <v>18.1</v>
@@ -7519,37 +7519,37 @@
         <v>21.35</v>
       </c>
       <c r="M76">
-        <v>24.7898224</v>
+        <v>25.12482</v>
       </c>
       <c r="N76">
-        <v>-3.439822400000001</v>
+        <v>-3.774819999999998</v>
       </c>
       <c r="O76">
-        <v>-0.9287520480000002</v>
+        <v>-1.0192014</v>
       </c>
       <c r="P76">
-        <v>-2.511070352</v>
+        <v>-2.755618599999999</v>
       </c>
       <c r="Q76">
-        <v>8.888929647999998</v>
+        <v>8.6443814</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1481540464155753</v>
+        <v>0.1522482082721983</v>
       </c>
       <c r="T76">
-        <v>1.87465030535764</v>
+        <v>1.949636317571946</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2325349454702023</v>
+        <v>0.2294344795305996</v>
       </c>
       <c r="W76">
-        <v>0.1126638700049743</v>
+        <v>0.113119018404908</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8612405387785271</v>
+        <v>0.8497573315948135</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1229013158717306</v>
+        <v>0.1239113158717306</v>
       </c>
       <c r="C77">
-        <v>-51.50482980017355</v>
+        <v>-54.87407588758788</v>
       </c>
       <c r="D77">
-        <v>101.5451701998264</v>
+        <v>100.4579241124121</v>
       </c>
       <c r="E77">
-        <v>50.54999999999998</v>
+        <v>52.83199999999999</v>
       </c>
       <c r="F77">
-        <v>171.15</v>
+        <v>173.432</v>
       </c>
       <c r="G77">
         <v>18.1</v>
@@ -7601,37 +7601,37 @@
         <v>21.35</v>
       </c>
       <c r="M77">
-        <v>25.12482</v>
+        <v>25.4598176</v>
       </c>
       <c r="N77">
-        <v>-3.774819999999998</v>
+        <v>-4.1098176</v>
       </c>
       <c r="O77">
-        <v>-1.0192014</v>
+        <v>-1.109650752</v>
       </c>
       <c r="P77">
-        <v>-2.755618599999999</v>
+        <v>-3.000166848</v>
       </c>
       <c r="Q77">
-        <v>8.6443814</v>
+        <v>8.399833151999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1522482082721983</v>
+        <v>0.1566835502835399</v>
       </c>
       <c r="T77">
-        <v>1.949636317571946</v>
+        <v>2.030871164137444</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2294344795305996</v>
+        <v>0.2264156047999339</v>
       </c>
       <c r="W77">
-        <v>0.113119018404908</v>
+        <v>0.1135621892153697</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8497573315948135</v>
+        <v>0.838576314073829</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1239113158717306</v>
+        <v>0.1249213158717306</v>
       </c>
       <c r="C78">
-        <v>-54.87407588758788</v>
+        <v>-58.22028628905895</v>
       </c>
       <c r="D78">
-        <v>100.4579241124121</v>
+        <v>99.39371371094106</v>
       </c>
       <c r="E78">
-        <v>52.83199999999999</v>
+        <v>55.114</v>
       </c>
       <c r="F78">
-        <v>173.432</v>
+        <v>175.714</v>
       </c>
       <c r="G78">
         <v>18.1</v>
@@ -7683,37 +7683,37 @@
         <v>21.35</v>
       </c>
       <c r="M78">
-        <v>25.4598176</v>
+        <v>25.7948152</v>
       </c>
       <c r="N78">
-        <v>-4.1098176</v>
+        <v>-4.444815200000001</v>
       </c>
       <c r="O78">
-        <v>-1.109650752</v>
+        <v>-1.200100104</v>
       </c>
       <c r="P78">
-        <v>-3.000166848</v>
+        <v>-3.244715096</v>
       </c>
       <c r="Q78">
-        <v>8.399833151999999</v>
+        <v>8.155284903999998</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1566835502835399</v>
+        <v>0.1615045742089112</v>
       </c>
       <c r="T78">
-        <v>2.030871164137444</v>
+        <v>2.11916991040429</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2264156047999339</v>
+        <v>0.2234751423999347</v>
       </c>
       <c r="W78">
-        <v>0.1135621892153697</v>
+        <v>0.1139938490956896</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.838576314073829</v>
+        <v>0.8276857125923507</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1249213158717306</v>
+        <v>0.1259313158717305</v>
       </c>
       <c r="C79">
-        <v>-58.22028628905895</v>
+        <v>-61.54418542246961</v>
       </c>
       <c r="D79">
-        <v>99.39371371094106</v>
+        <v>98.35181457753039</v>
       </c>
       <c r="E79">
-        <v>55.114</v>
+        <v>57.39600000000002</v>
       </c>
       <c r="F79">
-        <v>175.714</v>
+        <v>177.996</v>
       </c>
       <c r="G79">
         <v>18.1</v>
@@ -7765,37 +7765,37 @@
         <v>21.35</v>
       </c>
       <c r="M79">
-        <v>25.7948152</v>
+        <v>26.1298128</v>
       </c>
       <c r="N79">
-        <v>-4.444815200000001</v>
+        <v>-4.779812800000002</v>
       </c>
       <c r="O79">
-        <v>-1.200100104</v>
+        <v>-1.290549456000001</v>
       </c>
       <c r="P79">
-        <v>-3.244715096</v>
+        <v>-3.489263344000001</v>
       </c>
       <c r="Q79">
-        <v>8.155284903999998</v>
+        <v>7.910736655999997</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1615045742089112</v>
+        <v>0.1667638730365889</v>
       </c>
       <c r="T79">
-        <v>2.11916991040429</v>
+        <v>2.215495815422666</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2234751423999347</v>
+        <v>0.2206100764717304</v>
       </c>
       <c r="W79">
-        <v>0.1139938490956896</v>
+        <v>0.11441444077395</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8276857125923507</v>
+        <v>0.8170743573027052</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1259313158717305</v>
+        <v>0.1269413158717305</v>
       </c>
       <c r="C80">
-        <v>-61.54418542246961</v>
+        <v>-64.84646764583297</v>
       </c>
       <c r="D80">
-        <v>98.35181457753039</v>
+        <v>97.33153235416702</v>
       </c>
       <c r="E80">
-        <v>57.39600000000002</v>
+        <v>59.678</v>
       </c>
       <c r="F80">
-        <v>177.996</v>
+        <v>180.278</v>
       </c>
       <c r="G80">
         <v>18.1</v>
@@ -7847,37 +7847,37 @@
         <v>21.35</v>
       </c>
       <c r="M80">
-        <v>26.1298128</v>
+        <v>26.4648104</v>
       </c>
       <c r="N80">
-        <v>-4.779812800000002</v>
+        <v>-5.1148104</v>
       </c>
       <c r="O80">
-        <v>-1.290549456000001</v>
+        <v>-1.380998808</v>
       </c>
       <c r="P80">
-        <v>-3.489263344000001</v>
+        <v>-3.733811591999999</v>
       </c>
       <c r="Q80">
-        <v>7.910736655999997</v>
+        <v>7.666188407999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1667638730365889</v>
+        <v>0.1725240574669027</v>
       </c>
       <c r="T80">
-        <v>2.215495815422666</v>
+        <v>2.320995616157079</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2206100764717304</v>
+        <v>0.2178175438581642</v>
       </c>
       <c r="W80">
-        <v>0.11441444077395</v>
+        <v>0.1148243845616215</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8170743573027052</v>
+        <v>0.8067316439191267</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1269413158717305</v>
+        <v>0.1726387502603567</v>
       </c>
       <c r="C81">
-        <v>-64.84646764583297</v>
+        <v>-98.21934634845519</v>
       </c>
       <c r="D81">
-        <v>97.33153235416702</v>
+        <v>66.24065365154482</v>
       </c>
       <c r="E81">
-        <v>59.678</v>
+        <v>61.96000000000001</v>
       </c>
       <c r="F81">
-        <v>180.278</v>
+        <v>182.56</v>
       </c>
       <c r="G81">
         <v>18.1</v>
@@ -7929,45 +7929,45 @@
         <v>21.35</v>
       </c>
       <c r="M81">
-        <v>26.4648104</v>
+        <v>36.658048</v>
       </c>
       <c r="N81">
-        <v>-5.1148104</v>
+        <v>-15.308048</v>
       </c>
       <c r="O81">
-        <v>-1.380998808</v>
+        <v>-4.13317296</v>
       </c>
       <c r="P81">
-        <v>-3.733811591999999</v>
+        <v>-11.17487504</v>
       </c>
       <c r="Q81">
-        <v>7.666188407999999</v>
+        <v>0.2251249599999987</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1725240574669027</v>
+        <v>0.1862974322833786</v>
       </c>
       <c r="T81">
-        <v>2.320995616157079</v>
+        <v>2.573259812930278</v>
       </c>
       <c r="U81">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.2178175438581642</v>
+        <v>0.1572505988316672</v>
       </c>
       <c r="W81">
-        <v>0.1148243845616215</v>
+        <v>0.1692240797546012</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.8067316439191267</v>
+        <v>0.5824096253024711</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1726387502603567</v>
+        <v>0.1741887502603567</v>
       </c>
       <c r="C82">
-        <v>-98.21934634845519</v>
+        <v>-101.2113551904298</v>
       </c>
       <c r="D82">
-        <v>66.24065365154482</v>
+        <v>65.53064480957025</v>
       </c>
       <c r="E82">
-        <v>61.96000000000001</v>
+        <v>64.24200000000002</v>
       </c>
       <c r="F82">
-        <v>182.56</v>
+        <v>184.842</v>
       </c>
       <c r="G82">
         <v>18.1</v>
@@ -8011,37 +8011,37 @@
         <v>21.35</v>
       </c>
       <c r="M82">
-        <v>36.658048</v>
+        <v>37.11627360000001</v>
       </c>
       <c r="N82">
-        <v>-15.308048</v>
+        <v>-15.76627360000001</v>
       </c>
       <c r="O82">
-        <v>-4.13317296</v>
+        <v>-4.256893872000002</v>
       </c>
       <c r="P82">
-        <v>-11.17487504</v>
+        <v>-11.509379728</v>
       </c>
       <c r="Q82">
-        <v>0.2251249599999987</v>
+        <v>-0.109379728000004</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1862974322833786</v>
+        <v>0.1936920339825038</v>
       </c>
       <c r="T82">
-        <v>2.573259812930278</v>
+        <v>2.708694539926609</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1572505988316672</v>
+        <v>0.1553092334139923</v>
       </c>
       <c r="W82">
-        <v>0.1692240797546012</v>
+        <v>0.1696139059304703</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5824096253024711</v>
+        <v>0.5752193830147863</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1741887502603567</v>
+        <v>0.1757387502603567</v>
       </c>
       <c r="C83">
-        <v>-101.2113551904298</v>
+        <v>-104.188304807091</v>
       </c>
       <c r="D83">
-        <v>65.53064480957025</v>
+        <v>64.83569519290897</v>
       </c>
       <c r="E83">
-        <v>64.24200000000002</v>
+        <v>66.524</v>
       </c>
       <c r="F83">
-        <v>184.842</v>
+        <v>187.124</v>
       </c>
       <c r="G83">
         <v>18.1</v>
@@ -8093,37 +8093,37 @@
         <v>21.35</v>
       </c>
       <c r="M83">
-        <v>37.11627360000001</v>
+        <v>37.5744992</v>
       </c>
       <c r="N83">
-        <v>-15.76627360000001</v>
+        <v>-16.2244992</v>
       </c>
       <c r="O83">
-        <v>-4.256893872000002</v>
+        <v>-4.380614784</v>
       </c>
       <c r="P83">
-        <v>-11.509379728</v>
+        <v>-11.843884416</v>
       </c>
       <c r="Q83">
-        <v>-0.109379728000004</v>
+        <v>-0.4438844159999995</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1936920339825038</v>
+        <v>0.201908258092643</v>
       </c>
       <c r="T83">
-        <v>2.708694539926609</v>
+        <v>2.859177569922531</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1553092334139923</v>
+        <v>0.1534152183723583</v>
       </c>
       <c r="W83">
-        <v>0.1696139059304703</v>
+        <v>0.1699942241508305</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5752193830147863</v>
+        <v>0.5682045124902158</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1757387502603567</v>
+        <v>0.1772887502603567</v>
       </c>
       <c r="C84">
-        <v>-104.188304807091</v>
+        <v>-107.1506692781185</v>
       </c>
       <c r="D84">
-        <v>64.83569519290897</v>
+        <v>64.15533072188154</v>
       </c>
       <c r="E84">
-        <v>66.524</v>
+        <v>68.80600000000001</v>
       </c>
       <c r="F84">
-        <v>187.124</v>
+        <v>189.406</v>
       </c>
       <c r="G84">
         <v>18.1</v>
@@ -8175,37 +8175,37 @@
         <v>21.35</v>
       </c>
       <c r="M84">
-        <v>37.5744992</v>
+        <v>38.0327248</v>
       </c>
       <c r="N84">
-        <v>-16.2244992</v>
+        <v>-16.6827248</v>
       </c>
       <c r="O84">
-        <v>-4.380614784</v>
+        <v>-4.504335696000001</v>
       </c>
       <c r="P84">
-        <v>-11.843884416</v>
+        <v>-12.178389104</v>
       </c>
       <c r="Q84">
-        <v>-0.4438844159999995</v>
+        <v>-0.7783891040000022</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.201908258092643</v>
+        <v>0.2110910968039749</v>
       </c>
       <c r="T84">
-        <v>2.859177569922531</v>
+        <v>3.027364485800327</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1534152183723583</v>
+        <v>0.1515668422473901</v>
       </c>
       <c r="W84">
-        <v>0.1699942241508305</v>
+        <v>0.1703653780767241</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5682045124902158</v>
+        <v>0.5613586749903335</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1772887502603567</v>
+        <v>0.1788387502603567</v>
       </c>
       <c r="C85">
-        <v>-107.1506692781185</v>
+        <v>-110.0989029904949</v>
       </c>
       <c r="D85">
-        <v>64.15533072188154</v>
+        <v>63.48909700950507</v>
       </c>
       <c r="E85">
-        <v>68.80600000000001</v>
+        <v>71.08800000000002</v>
       </c>
       <c r="F85">
-        <v>189.406</v>
+        <v>191.688</v>
       </c>
       <c r="G85">
         <v>18.1</v>
@@ -8257,37 +8257,37 @@
         <v>21.35</v>
       </c>
       <c r="M85">
-        <v>38.0327248</v>
+        <v>38.4909504</v>
       </c>
       <c r="N85">
-        <v>-16.6827248</v>
+        <v>-17.1409504</v>
       </c>
       <c r="O85">
-        <v>-4.504335696000001</v>
+        <v>-4.628056608000001</v>
       </c>
       <c r="P85">
-        <v>-12.178389104</v>
+        <v>-12.512893792</v>
       </c>
       <c r="Q85">
-        <v>-0.7783891040000022</v>
+        <v>-1.112893792000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2110910968039749</v>
+        <v>0.2214217903542234</v>
       </c>
       <c r="T85">
-        <v>3.027364485800327</v>
+        <v>3.216574766162849</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1515668422473901</v>
+        <v>0.1497624750777783</v>
       </c>
       <c r="W85">
-        <v>0.1703653780767241</v>
+        <v>0.1707276950043821</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5613586749903335</v>
+        <v>0.554675833621401</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1788387502603567</v>
+        <v>0.1803887502603567</v>
       </c>
       <c r="C86">
-        <v>-110.0989029904949</v>
+        <v>-113.0334416505109</v>
       </c>
       <c r="D86">
-        <v>63.48909700950509</v>
+        <v>62.83655834948909</v>
       </c>
       <c r="E86">
-        <v>71.08799999999999</v>
+        <v>73.37</v>
       </c>
       <c r="F86">
-        <v>191.688</v>
+        <v>193.97</v>
       </c>
       <c r="G86">
         <v>18.1</v>
@@ -8339,37 +8339,37 @@
         <v>21.35</v>
       </c>
       <c r="M86">
-        <v>38.4909504</v>
+        <v>38.949176</v>
       </c>
       <c r="N86">
-        <v>-17.14095039999999</v>
+        <v>-17.599176</v>
       </c>
       <c r="O86">
-        <v>-4.628056607999999</v>
+        <v>-4.75177752</v>
       </c>
       <c r="P86">
-        <v>-12.512893792</v>
+        <v>-12.84739848</v>
       </c>
       <c r="Q86">
-        <v>-1.112893791999998</v>
+        <v>-1.44739848</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2214217903542232</v>
+        <v>0.2331299097111715</v>
       </c>
       <c r="T86">
-        <v>3.216574766162846</v>
+        <v>3.431013083907036</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1497624750777783</v>
+        <v>0.148000563606275</v>
       </c>
       <c r="W86">
-        <v>0.1707276950043821</v>
+        <v>0.17108148682786</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5546758336214012</v>
+        <v>0.5481502355787964</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1803887502603567</v>
+        <v>0.1819387502603567</v>
       </c>
       <c r="C87">
-        <v>-113.0334416505109</v>
+        <v>-115.9547032339956</v>
       </c>
       <c r="D87">
-        <v>62.83655834948909</v>
+        <v>62.19729676600443</v>
       </c>
       <c r="E87">
-        <v>73.37</v>
+        <v>75.65199999999999</v>
       </c>
       <c r="F87">
-        <v>193.97</v>
+        <v>196.252</v>
       </c>
       <c r="G87">
         <v>18.1</v>
@@ -8421,37 +8421,37 @@
         <v>21.35</v>
       </c>
       <c r="M87">
-        <v>38.949176</v>
+        <v>39.4074016</v>
       </c>
       <c r="N87">
-        <v>-17.599176</v>
+        <v>-18.0574016</v>
       </c>
       <c r="O87">
-        <v>-4.75177752</v>
+        <v>-4.875498432</v>
       </c>
       <c r="P87">
-        <v>-12.84739848</v>
+        <v>-13.181903168</v>
       </c>
       <c r="Q87">
-        <v>-1.44739848</v>
+        <v>-1.781903167999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2331299097111715</v>
+        <v>0.2465106175476837</v>
       </c>
       <c r="T87">
-        <v>3.431013083907036</v>
+        <v>3.676085447043253</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.148000563606275</v>
+        <v>0.1462796268201556</v>
       </c>
       <c r="W87">
-        <v>0.17108148682786</v>
+        <v>0.1714270509345128</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5481502355787964</v>
+        <v>0.5417763956302057</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1819387502603567</v>
+        <v>0.1834887502603567</v>
       </c>
       <c r="C88">
-        <v>-115.9547032339956</v>
+        <v>-118.8630888791292</v>
       </c>
       <c r="D88">
-        <v>62.19729676600443</v>
+        <v>61.57091112087083</v>
       </c>
       <c r="E88">
-        <v>75.65199999999999</v>
+        <v>77.934</v>
       </c>
       <c r="F88">
-        <v>196.252</v>
+        <v>198.534</v>
       </c>
       <c r="G88">
         <v>18.1</v>
@@ -8503,37 +8503,37 @@
         <v>21.35</v>
       </c>
       <c r="M88">
-        <v>39.4074016</v>
+        <v>39.8656272</v>
       </c>
       <c r="N88">
-        <v>-18.0574016</v>
+        <v>-18.5156272</v>
       </c>
       <c r="O88">
-        <v>-4.875498432</v>
+        <v>-4.999219343999999</v>
       </c>
       <c r="P88">
-        <v>-13.181903168</v>
+        <v>-13.516407856</v>
       </c>
       <c r="Q88">
-        <v>-1.781903167999999</v>
+        <v>-2.116407855999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2465106175476837</v>
+        <v>0.2619498958205824</v>
       </c>
       <c r="T88">
-        <v>3.676085447043253</v>
+        <v>3.958861250661965</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1462796268201556</v>
+        <v>0.1445982517992342</v>
       </c>
       <c r="W88">
-        <v>0.1714270509345128</v>
+        <v>0.1717646710387138</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5417763956302057</v>
+        <v>0.5355490807379045</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1834887502603567</v>
+        <v>0.1850387502603567</v>
       </c>
       <c r="C89">
-        <v>-118.8630888791292</v>
+        <v>-121.758983725845</v>
       </c>
       <c r="D89">
-        <v>61.57091112087083</v>
+        <v>60.95701627415496</v>
       </c>
       <c r="E89">
-        <v>77.934</v>
+        <v>80.21600000000001</v>
       </c>
       <c r="F89">
-        <v>198.534</v>
+        <v>200.816</v>
       </c>
       <c r="G89">
         <v>18.1</v>
@@ -8585,37 +8585,37 @@
         <v>21.35</v>
       </c>
       <c r="M89">
-        <v>39.8656272</v>
+        <v>40.3238528</v>
       </c>
       <c r="N89">
-        <v>-18.5156272</v>
+        <v>-18.9738528</v>
       </c>
       <c r="O89">
-        <v>-4.999219343999999</v>
+        <v>-5.122940256000001</v>
       </c>
       <c r="P89">
-        <v>-13.516407856</v>
+        <v>-13.850912544</v>
       </c>
       <c r="Q89">
-        <v>-2.116407855999999</v>
+        <v>-2.450912544000003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2619498958205824</v>
+        <v>0.2799623871389644</v>
       </c>
       <c r="T89">
-        <v>3.958861250661965</v>
+        <v>4.288766354883797</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1445982517992342</v>
+        <v>0.1429550898469702</v>
       </c>
       <c r="W89">
-        <v>0.1717646710387138</v>
+        <v>0.1720946179587284</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5355490807379045</v>
+        <v>0.5294632957295191</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1850387502603567</v>
+        <v>0.1865887502603567</v>
       </c>
       <c r="C90">
-        <v>-121.758983725845</v>
+        <v>-124.6427577055111</v>
       </c>
       <c r="D90">
-        <v>60.95701627415496</v>
+        <v>60.3552422944889</v>
       </c>
       <c r="E90">
-        <v>80.21600000000001</v>
+        <v>82.49799999999999</v>
       </c>
       <c r="F90">
-        <v>200.816</v>
+        <v>203.098</v>
       </c>
       <c r="G90">
         <v>18.1</v>
@@ -8667,37 +8667,37 @@
         <v>21.35</v>
       </c>
       <c r="M90">
-        <v>40.3238528</v>
+        <v>40.7820784</v>
       </c>
       <c r="N90">
-        <v>-18.9738528</v>
+        <v>-19.43207839999999</v>
       </c>
       <c r="O90">
-        <v>-5.122940256000001</v>
+        <v>-5.246661167999999</v>
       </c>
       <c r="P90">
-        <v>-13.850912544</v>
+        <v>-14.185417232</v>
       </c>
       <c r="Q90">
-        <v>-2.450912544000003</v>
+        <v>-2.785417231999997</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2799623871389644</v>
+        <v>0.3012498768788702</v>
       </c>
       <c r="T90">
-        <v>4.288766354883797</v>
+        <v>4.678654205327778</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1429550898469702</v>
+        <v>0.1413488528823975</v>
       </c>
       <c r="W90">
-        <v>0.1720946179587284</v>
+        <v>0.1724171503412146</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5294632957295191</v>
+        <v>0.5235142699348055</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1865887502603567</v>
+        <v>0.1881387502603567</v>
       </c>
       <c r="C91">
-        <v>-124.6427577055111</v>
+        <v>-127.5147662842942</v>
       </c>
       <c r="D91">
-        <v>60.3552422944889</v>
+        <v>59.76523371570578</v>
       </c>
       <c r="E91">
-        <v>82.49799999999999</v>
+        <v>84.78</v>
       </c>
       <c r="F91">
-        <v>203.098</v>
+        <v>205.38</v>
       </c>
       <c r="G91">
         <v>18.1</v>
@@ -8749,37 +8749,37 @@
         <v>21.35</v>
       </c>
       <c r="M91">
-        <v>40.7820784</v>
+        <v>41.240304</v>
       </c>
       <c r="N91">
-        <v>-19.43207839999999</v>
+        <v>-19.890304</v>
       </c>
       <c r="O91">
-        <v>-5.246661167999999</v>
+        <v>-5.370382080000001</v>
       </c>
       <c r="P91">
-        <v>-14.185417232</v>
+        <v>-14.51992192</v>
       </c>
       <c r="Q91">
-        <v>-2.785417231999997</v>
+        <v>-3.119921920000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3012498768788702</v>
+        <v>0.3267948645667573</v>
       </c>
       <c r="T91">
-        <v>4.678654205327778</v>
+        <v>5.146519625860556</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1413488528823975</v>
+        <v>0.1397783100725931</v>
       </c>
       <c r="W91">
-        <v>0.1724171503412146</v>
+        <v>0.1727325153374233</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5235142699348055</v>
+        <v>0.5176974447133076</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1881387502603567</v>
+        <v>0.1896887502603567</v>
       </c>
       <c r="C92">
-        <v>-127.5147662842942</v>
+        <v>-130.3753511633452</v>
       </c>
       <c r="D92">
-        <v>59.76523371570578</v>
+        <v>59.18664883665478</v>
       </c>
       <c r="E92">
-        <v>84.78</v>
+        <v>87.06200000000001</v>
       </c>
       <c r="F92">
-        <v>205.38</v>
+        <v>207.662</v>
       </c>
       <c r="G92">
         <v>18.1</v>
@@ -8831,37 +8831,37 @@
         <v>21.35</v>
       </c>
       <c r="M92">
-        <v>41.240304</v>
+        <v>41.6985296</v>
       </c>
       <c r="N92">
-        <v>-19.890304</v>
+        <v>-20.3485296</v>
       </c>
       <c r="O92">
-        <v>-5.370382080000001</v>
+        <v>-5.494102992</v>
       </c>
       <c r="P92">
-        <v>-14.51992192</v>
+        <v>-14.854426608</v>
       </c>
       <c r="Q92">
-        <v>-3.119921920000001</v>
+        <v>-3.454426608</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3267948645667573</v>
+        <v>0.3580165161852859</v>
       </c>
       <c r="T92">
-        <v>5.146519625860556</v>
+        <v>5.718355139845062</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1397783100725931</v>
+        <v>0.13824228468718</v>
       </c>
       <c r="W92">
-        <v>0.1727325153374233</v>
+        <v>0.1730409492348143</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5176974447133076</v>
+        <v>0.5120084618043702</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1896887502603567</v>
+        <v>0.1912387502603567</v>
       </c>
       <c r="C93">
-        <v>-130.3753511633452</v>
+        <v>-133.2248409387034</v>
       </c>
       <c r="D93">
-        <v>59.18664883665478</v>
+        <v>58.61915906129664</v>
       </c>
       <c r="E93">
-        <v>87.06200000000001</v>
+        <v>89.34399999999999</v>
       </c>
       <c r="F93">
-        <v>207.662</v>
+        <v>209.944</v>
       </c>
       <c r="G93">
         <v>18.1</v>
@@ -8913,37 +8913,37 @@
         <v>21.35</v>
       </c>
       <c r="M93">
-        <v>41.6985296</v>
+        <v>42.1567552</v>
       </c>
       <c r="N93">
-        <v>-20.3485296</v>
+        <v>-20.8067552</v>
       </c>
       <c r="O93">
-        <v>-5.494102992</v>
+        <v>-5.617823904</v>
       </c>
       <c r="P93">
-        <v>-14.854426608</v>
+        <v>-15.188931296</v>
       </c>
       <c r="Q93">
-        <v>-3.454426608</v>
+        <v>-3.788931295999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3580165161852859</v>
+        <v>0.3970435807084468</v>
       </c>
       <c r="T93">
-        <v>5.718355139845062</v>
+        <v>6.433149532325698</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.13824228468718</v>
+        <v>0.1367396511579715</v>
       </c>
       <c r="W93">
-        <v>0.1730409492348143</v>
+        <v>0.1733426780474793</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5120084618043702</v>
+        <v>0.5064431524369315</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1912387502603567</v>
+        <v>0.1927887502603567</v>
       </c>
       <c r="C94">
-        <v>-133.2248409387034</v>
+        <v>-136.0635517235976</v>
       </c>
       <c r="D94">
-        <v>58.61915906129664</v>
+        <v>58.06244827640235</v>
       </c>
       <c r="E94">
-        <v>89.34399999999999</v>
+        <v>91.626</v>
       </c>
       <c r="F94">
-        <v>209.944</v>
+        <v>212.226</v>
       </c>
       <c r="G94">
         <v>18.1</v>
@@ -8995,37 +8995,37 @@
         <v>21.35</v>
       </c>
       <c r="M94">
-        <v>42.1567552</v>
+        <v>42.6149808</v>
       </c>
       <c r="N94">
-        <v>-20.8067552</v>
+        <v>-21.2649808</v>
       </c>
       <c r="O94">
-        <v>-5.617823904</v>
+        <v>-5.741544815999999</v>
       </c>
       <c r="P94">
-        <v>-15.188931296</v>
+        <v>-15.523435984</v>
       </c>
       <c r="Q94">
-        <v>-3.788931295999999</v>
+        <v>-4.123435983999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3970435807084468</v>
+        <v>0.4472212350953677</v>
       </c>
       <c r="T94">
-        <v>6.433149532325698</v>
+        <v>7.352170894086512</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1367396511579715</v>
+        <v>0.1352693323283159</v>
       </c>
       <c r="W94">
-        <v>0.1733426780474793</v>
+        <v>0.1736379180684742</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5064431524369315</v>
+        <v>0.5009975271419107</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1927887502603567</v>
+        <v>0.2278389480023824</v>
       </c>
       <c r="C95">
-        <v>-136.0635517235976</v>
+        <v>-148.6104463314857</v>
       </c>
       <c r="D95">
-        <v>58.06244827640235</v>
+        <v>47.79755366851426</v>
       </c>
       <c r="E95">
-        <v>91.626</v>
+        <v>93.90800000000002</v>
       </c>
       <c r="F95">
-        <v>212.226</v>
+        <v>214.508</v>
       </c>
       <c r="G95">
         <v>18.1</v>
@@ -9077,45 +9077,45 @@
         <v>21.35</v>
       </c>
       <c r="M95">
-        <v>42.6149808</v>
+        <v>50.58098640000001</v>
       </c>
       <c r="N95">
-        <v>-21.2649808</v>
+        <v>-29.23098640000001</v>
       </c>
       <c r="O95">
-        <v>-5.741544815999999</v>
+        <v>-7.892366328000002</v>
       </c>
       <c r="P95">
-        <v>-15.523435984</v>
+        <v>-21.338620072</v>
       </c>
       <c r="Q95">
-        <v>-4.123435983999999</v>
+        <v>-9.938620072000006</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4472212350953677</v>
+        <v>0.5241280699783568</v>
       </c>
       <c r="T95">
-        <v>7.352170894086512</v>
+        <v>8.760746583533278</v>
       </c>
       <c r="U95">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1352693323283159</v>
+        <v>0.1139657489953577</v>
       </c>
       <c r="W95">
-        <v>0.1736379180684742</v>
+        <v>0.2089268763868947</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.5009975271419107</v>
+        <v>0.4220953666494728</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2278389480023824</v>
+        <v>0.2297389480023824</v>
       </c>
       <c r="C96">
-        <v>-148.6104463314857</v>
+        <v>-151.3461640314957</v>
       </c>
       <c r="D96">
-        <v>47.79755366851426</v>
+        <v>47.34383596850426</v>
       </c>
       <c r="E96">
-        <v>93.90800000000002</v>
+        <v>96.19</v>
       </c>
       <c r="F96">
-        <v>214.508</v>
+        <v>216.79</v>
       </c>
       <c r="G96">
         <v>18.1</v>
@@ -9159,37 +9159,37 @@
         <v>21.35</v>
       </c>
       <c r="M96">
-        <v>50.58098640000001</v>
+        <v>51.119082</v>
       </c>
       <c r="N96">
-        <v>-29.23098640000001</v>
+        <v>-29.769082</v>
       </c>
       <c r="O96">
-        <v>-7.892366328000002</v>
+        <v>-8.037652140000001</v>
       </c>
       <c r="P96">
-        <v>-21.338620072</v>
+        <v>-21.73142986</v>
       </c>
       <c r="Q96">
-        <v>-9.938620072000006</v>
+        <v>-10.33142986</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5241280699783568</v>
+        <v>0.6197936839740286</v>
       </c>
       <c r="T96">
-        <v>8.760746583533278</v>
+        <v>10.51289590023994</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1139657489953577</v>
+        <v>0.1127661095322487</v>
       </c>
       <c r="W96">
-        <v>0.2089268763868947</v>
+        <v>0.2092097513722958</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4220953666494728</v>
+        <v>0.4176522575268469</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2297389480023824</v>
+        <v>0.2316389480023824</v>
       </c>
       <c r="C97">
-        <v>-151.3461640314957</v>
+        <v>-154.0733489096561</v>
       </c>
       <c r="D97">
-        <v>47.34383596850426</v>
+        <v>46.89865109034389</v>
       </c>
       <c r="E97">
-        <v>96.19</v>
+        <v>98.47200000000001</v>
       </c>
       <c r="F97">
-        <v>216.79</v>
+        <v>219.072</v>
       </c>
       <c r="G97">
         <v>18.1</v>
@@ -9241,37 +9241,37 @@
         <v>21.35</v>
       </c>
       <c r="M97">
-        <v>51.119082</v>
+        <v>51.6571776</v>
       </c>
       <c r="N97">
-        <v>-29.769082</v>
+        <v>-30.3071776</v>
       </c>
       <c r="O97">
-        <v>-8.037652140000001</v>
+        <v>-8.182937952000001</v>
       </c>
       <c r="P97">
-        <v>-21.73142986</v>
+        <v>-22.124239648</v>
       </c>
       <c r="Q97">
-        <v>-10.33142986</v>
+        <v>-10.724239648</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6197936839740286</v>
+        <v>0.763292104967536</v>
       </c>
       <c r="T97">
-        <v>10.51289590023994</v>
+        <v>13.14111987529993</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1127661095322487</v>
+        <v>0.1115914625579544</v>
       </c>
       <c r="W97">
-        <v>0.2092097513722958</v>
+        <v>0.2094867331288344</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4176522575268469</v>
+        <v>0.4133017131776088</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2316389480023824</v>
+        <v>0.2335389480023824</v>
       </c>
       <c r="C98">
-        <v>-154.0733489096561</v>
+        <v>-156.7922394318229</v>
       </c>
       <c r="D98">
-        <v>46.89865109034389</v>
+        <v>46.46176056817705</v>
       </c>
       <c r="E98">
-        <v>98.47199999999998</v>
+        <v>100.754</v>
       </c>
       <c r="F98">
-        <v>219.072</v>
+        <v>221.354</v>
       </c>
       <c r="G98">
         <v>18.1</v>
@@ -9323,37 +9323,37 @@
         <v>21.35</v>
       </c>
       <c r="M98">
-        <v>51.6571776</v>
+        <v>52.1952732</v>
       </c>
       <c r="N98">
-        <v>-30.3071776</v>
+        <v>-30.84527319999999</v>
       </c>
       <c r="O98">
-        <v>-8.182937952</v>
+        <v>-8.328223763999999</v>
       </c>
       <c r="P98">
-        <v>-22.124239648</v>
+        <v>-22.51704943599999</v>
       </c>
       <c r="Q98">
-        <v>-10.724239648</v>
+        <v>-11.11704943599999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.763292104967534</v>
+        <v>1.002456139956712</v>
       </c>
       <c r="T98">
-        <v>13.14111987529989</v>
+        <v>17.52149316706652</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1115914625579544</v>
+        <v>0.1104410351089033</v>
       </c>
       <c r="W98">
-        <v>0.2094867331288344</v>
+        <v>0.2097580039213206</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4133017131776089</v>
+        <v>0.409040870773716</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2335389480023824</v>
+        <v>0.2354389480023824</v>
       </c>
       <c r="C99">
-        <v>-156.7922394318229</v>
+        <v>-159.5030652600259</v>
       </c>
       <c r="D99">
-        <v>46.46176056817705</v>
+        <v>46.03293473997408</v>
       </c>
       <c r="E99">
-        <v>100.754</v>
+        <v>103.036</v>
       </c>
       <c r="F99">
-        <v>221.354</v>
+        <v>223.636</v>
       </c>
       <c r="G99">
         <v>18.1</v>
@@ -9405,37 +9405,37 @@
         <v>21.35</v>
       </c>
       <c r="M99">
-        <v>52.1952732</v>
+        <v>52.7333688</v>
       </c>
       <c r="N99">
-        <v>-30.84527319999999</v>
+        <v>-31.3833688</v>
       </c>
       <c r="O99">
-        <v>-8.328223763999999</v>
+        <v>-8.473509576</v>
       </c>
       <c r="P99">
-        <v>-22.51704943599999</v>
+        <v>-22.909859224</v>
       </c>
       <c r="Q99">
-        <v>-11.11704943599999</v>
+        <v>-11.509859224</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.002456139956712</v>
+        <v>1.480784209935068</v>
       </c>
       <c r="T99">
-        <v>17.52149316706652</v>
+        <v>26.28223975059979</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1104410351089033</v>
+        <v>0.1093140857710574</v>
       </c>
       <c r="W99">
-        <v>0.2097580039213206</v>
+        <v>0.2100237385751847</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.409040870773716</v>
+        <v>0.4048669843372495</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2354389480023824</v>
+        <v>0.2373389480023823</v>
       </c>
       <c r="C100">
-        <v>-159.5030652600259</v>
+        <v>-162.206047655034</v>
       </c>
       <c r="D100">
-        <v>46.03293473997408</v>
+        <v>45.61195234496599</v>
       </c>
       <c r="E100">
-        <v>103.036</v>
+        <v>105.318</v>
       </c>
       <c r="F100">
-        <v>223.636</v>
+        <v>225.918</v>
       </c>
       <c r="G100">
         <v>18.1</v>
@@ -9487,37 +9487,37 @@
         <v>21.35</v>
       </c>
       <c r="M100">
-        <v>52.7333688</v>
+        <v>53.2714644</v>
       </c>
       <c r="N100">
-        <v>-31.3833688</v>
+        <v>-31.9214644</v>
       </c>
       <c r="O100">
-        <v>-8.473509576</v>
+        <v>-8.618795388000001</v>
       </c>
       <c r="P100">
-        <v>-22.909859224</v>
+        <v>-23.302669012</v>
       </c>
       <c r="Q100">
-        <v>-11.509859224</v>
+        <v>-11.902669012</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.480784209935068</v>
+        <v>2.915768419870136</v>
       </c>
       <c r="T100">
-        <v>26.28223975059979</v>
+        <v>52.56447950119957</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1093140857710574</v>
+        <v>0.1082099030865012</v>
       </c>
       <c r="W100">
-        <v>0.2100237385751847</v>
+        <v>0.210284104852203</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4048669843372495</v>
+        <v>0.4007774188388934</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2373389480023823</v>
-      </c>
-      <c r="C101">
-        <v>-162.206047655034</v>
-      </c>
-      <c r="D101">
-        <v>45.61195234496599</v>
-      </c>
-      <c r="E101">
-        <v>105.318</v>
-      </c>
-      <c r="F101">
-        <v>225.918</v>
-      </c>
-      <c r="G101">
-        <v>18.1</v>
-      </c>
-      <c r="H101">
-        <v>107.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>32.75</v>
-      </c>
-      <c r="K101">
-        <v>11.4</v>
-      </c>
-      <c r="L101">
-        <v>21.35</v>
-      </c>
-      <c r="M101">
-        <v>53.2714644</v>
-      </c>
-      <c r="N101">
-        <v>-31.9214644</v>
-      </c>
-      <c r="O101">
-        <v>-8.618795388000001</v>
-      </c>
-      <c r="P101">
-        <v>-23.302669012</v>
-      </c>
-      <c r="Q101">
-        <v>-11.902669012</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.915768419870136</v>
-      </c>
-      <c r="T101">
-        <v>52.56447950119957</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1082099030865012</v>
-      </c>
-      <c r="W101">
-        <v>0.210284104852203</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4007774188388934</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
